--- a/model/Outputs/11. Interest rate/10/Output Files/0.1/Output_18_44.xlsx
+++ b/model/Outputs/11. Interest rate/10/Output Files/0.1/Output_18_44.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4945555.141111895</v>
+        <v>4945672.357467126</v>
       </c>
     </row>
     <row r="7">
@@ -654,10 +654,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>76.99931295557451</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>44.47457824299391</v>
+        <v>35.98443791955802</v>
       </c>
       <c r="D2" t="n">
         <v>5.339155739849787</v>
@@ -720,7 +720,7 @@
         <v>233.3734759809475</v>
       </c>
       <c r="X2" t="n">
-        <v>101.7923801816573</v>
+        <v>187.2818334606677</v>
       </c>
       <c r="Y2" t="n">
         <v>106.3174326828064</v>
@@ -745,46 +745,46 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>208.5358198536127</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>141.2296047131211</v>
+      </c>
+      <c r="R3" t="n">
         <v>334</v>
       </c>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>100.964735551489</v>
-      </c>
-      <c r="R3" t="n">
-        <v>126.7823255942661</v>
-      </c>
       <c r="S3" t="n">
-        <v>56.9294716627245</v>
+        <v>334</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
@@ -796,10 +796,10 @@
         <v>9.510667191520156</v>
       </c>
       <c r="W3" t="n">
-        <v>334</v>
+        <v>27.37314290982852</v>
       </c>
       <c r="X3" t="n">
-        <v>334</v>
+        <v>241.5379653319173</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
@@ -942,10 +942,10 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>79.22163513900631</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>94.14476161538256</v>
+        <v>173.3663967543888</v>
       </c>
       <c r="U5" t="n">
         <v>244.1839900159473</v>
@@ -985,7 +985,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>325.4900264410651</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
         <v>334</v>
       </c>
       <c r="S6" t="n">
-        <v>334</v>
+        <v>235.1851994454648</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -1033,7 +1033,7 @@
         <v>9.510667191520156</v>
       </c>
       <c r="W6" t="n">
-        <v>254.0483687963584</v>
+        <v>27.37314290982852</v>
       </c>
       <c r="X6" t="n">
         <v>14.86273944538755</v>
@@ -1207,16 +1207,16 @@
         </is>
       </c>
       <c r="B9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" t="n">
         <v>356</v>
       </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E9" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -1273,7 +1273,7 @@
         <v>27.37314290982852</v>
       </c>
       <c r="X9" t="n">
-        <v>321.0674907066267</v>
+        <v>315.8019010308367</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>162.9993129555745</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
         <v>130.4745782429939</v>
@@ -1380,10 +1380,10 @@
         <v>85.88962870801186</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>84.29104062872476</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>84.23383960805002</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -1416,7 +1416,7 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>165.2216351390063</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
         <v>0</v>
@@ -1425,16 +1425,16 @@
         <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>273.8875580238858</v>
       </c>
       <c r="W11" t="n">
-        <v>241.2475334642208</v>
+        <v>319.3734759809475</v>
       </c>
       <c r="X11" t="n">
         <v>273.2818334606677</v>
       </c>
       <c r="Y11" t="n">
-        <v>192.3174326828064</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1465,7 +1465,7 @@
         <v>10.75835133736453</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>176.3581706190965</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1504,7 +1504,7 @@
         <v>81.19394466584713</v>
       </c>
       <c r="V12" t="n">
-        <v>271.8688378106167</v>
+        <v>95.51066719152016</v>
       </c>
       <c r="W12" t="n">
         <v>113.3731429098285</v>
@@ -1553,19 +1553,19 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>73.4482183217136</v>
       </c>
       <c r="M13" t="n">
         <v>168.8416441894351</v>
       </c>
       <c r="N13" t="n">
-        <v>220.1747801897177</v>
+        <v>105.5328620172644</v>
       </c>
       <c r="O13" t="n">
-        <v>291.8788755544248</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>10.07591208704745</v>
+        <v>343.1484874922119</v>
       </c>
       <c r="Q13" t="n">
         <v>368</v>
@@ -1602,25 +1602,25 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>118.9993129555745</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>86.47457824299391</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>47.33915573984979</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>41.36328960686865</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>41.88962870801186</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>40.29104062872475</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>40.23383960805002</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -1653,22 +1653,22 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>121.2216351390063</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>221.634214894393</v>
       </c>
       <c r="U14" t="n">
-        <v>286.1839900159474</v>
+        <v>286.1839900159473</v>
       </c>
       <c r="V14" t="n">
-        <v>72.38682236955766</v>
+        <v>266.8510241668239</v>
       </c>
       <c r="W14" t="n">
         <v>275.3734759809475</v>
       </c>
       <c r="X14" t="n">
-        <v>229.2818334606677</v>
+        <v>108.5526271200755</v>
       </c>
       <c r="Y14" t="n">
         <v>148.3174326828064</v>
@@ -1684,7 +1684,7 @@
         <v>21.55655664632661</v>
       </c>
       <c r="C15" t="n">
-        <v>17.53150518360036</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -1729,28 +1729,28 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>368</v>
+        <v>168.7823255942661</v>
       </c>
       <c r="S15" t="n">
-        <v>98.92947166272451</v>
+        <v>98.9294716627245</v>
       </c>
       <c r="T15" t="n">
-        <v>41.35206710430627</v>
+        <v>41.35206710430629</v>
       </c>
       <c r="U15" t="n">
-        <v>368</v>
+        <v>240.6301688910276</v>
       </c>
       <c r="V15" t="n">
         <v>51.51066719152016</v>
       </c>
       <c r="W15" t="n">
+        <v>69.37314290982852</v>
+      </c>
+      <c r="X15" t="n">
         <v>368</v>
       </c>
-      <c r="X15" t="n">
-        <v>56.86273944538755</v>
-      </c>
       <c r="Y15" t="n">
-        <v>36.39139276613435</v>
+        <v>368</v>
       </c>
     </row>
     <row r="16">
@@ -1790,7 +1790,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>29.4482183217136</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
         <v>124.8416441894351</v>
@@ -1805,10 +1805,10 @@
         <v>299.1484874922119</v>
       </c>
       <c r="Q16" t="n">
-        <v>345.323266425598</v>
+        <v>225.8939927897808</v>
       </c>
       <c r="R16" t="n">
-        <v>205.3191278268988</v>
+        <v>354.1966197844298</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -1890,7 +1890,7 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>83.22163513900632</v>
+        <v>77.90158330834055</v>
       </c>
       <c r="T17" t="n">
         <v>183.634214894393</v>
@@ -1902,7 +1902,7 @@
         <v>228.8510241668239</v>
       </c>
       <c r="W17" t="n">
-        <v>232.0534241502819</v>
+        <v>237.3734759809475</v>
       </c>
       <c r="X17" t="n">
         <v>191.2818334606677</v>
@@ -1936,7 +1936,7 @@
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>329.7583513373645</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -1966,22 +1966,22 @@
         <v>141.2296047131211</v>
       </c>
       <c r="R18" t="n">
+        <v>130.7823255942661</v>
+      </c>
+      <c r="S18" t="n">
+        <v>68.14931180555431</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3.352067104306268</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
         <v>368</v>
       </c>
-      <c r="S18" t="n">
+      <c r="W18" t="n">
         <v>368</v>
-      </c>
-      <c r="T18" t="n">
-        <v>119.1582457401424</v>
-      </c>
-      <c r="U18" t="n">
-        <v>368</v>
-      </c>
-      <c r="V18" t="n">
-        <v>13.51066719152016</v>
-      </c>
-      <c r="W18" t="n">
-        <v>31.37314290982852</v>
       </c>
       <c r="X18" t="n">
         <v>18.86273944538755</v>
@@ -2091,10 +2091,10 @@
         <v>3.889628708011855</v>
       </c>
       <c r="G20" t="n">
-        <v>2.291040628724753</v>
+        <v>2.291040628724772</v>
       </c>
       <c r="H20" t="n">
-        <v>2.233839608050022</v>
+        <v>2.233839608050005</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -2127,13 +2127,13 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>83.22163513900632</v>
+        <v>83.22163513900631</v>
       </c>
       <c r="T20" t="n">
         <v>183.634214894393</v>
       </c>
       <c r="U20" t="n">
-        <v>242.8639381852816</v>
+        <v>248.1839900159473</v>
       </c>
       <c r="V20" t="n">
         <v>228.8510241668239</v>
@@ -2145,7 +2145,7 @@
         <v>191.2818334606677</v>
       </c>
       <c r="Y20" t="n">
-        <v>110.3174326828064</v>
+        <v>104.9973808521407</v>
       </c>
     </row>
     <row r="21">
@@ -2158,7 +2158,7 @@
         <v>368</v>
       </c>
       <c r="C21" t="n">
-        <v>323.467524288674</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -2206,10 +2206,10 @@
         <v>130.7823255942661</v>
       </c>
       <c r="S21" t="n">
-        <v>60.92947166272451</v>
+        <v>60.9294716627245</v>
       </c>
       <c r="T21" t="n">
-        <v>3.352067104306268</v>
+        <v>3.352067104306286</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
@@ -2218,7 +2218,7 @@
         <v>13.51066719152016</v>
       </c>
       <c r="W21" t="n">
-        <v>368</v>
+        <v>330.3676118431546</v>
       </c>
       <c r="X21" t="n">
         <v>18.86273944538755</v>
@@ -2267,7 +2267,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>86.84164418943513</v>
+        <v>86.8416441894351</v>
       </c>
       <c r="N22" t="n">
         <v>138.1747801897177</v>
@@ -2282,7 +2282,7 @@
         <v>307.323266425598</v>
       </c>
       <c r="R22" t="n">
-        <v>316.1966197844297</v>
+        <v>316.1966197844298</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -2328,10 +2328,10 @@
         <v>3.889628708011855</v>
       </c>
       <c r="G23" t="n">
-        <v>2.291040628724772</v>
+        <v>2.291040628724753</v>
       </c>
       <c r="H23" t="n">
-        <v>2.233839608050005</v>
+        <v>2.233839608050022</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -2370,7 +2370,7 @@
         <v>183.634214894393</v>
       </c>
       <c r="U23" t="n">
-        <v>248.1839900159473</v>
+        <v>248.1839900159474</v>
       </c>
       <c r="V23" t="n">
         <v>228.8510241668239</v>
@@ -2395,7 +2395,7 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>324.4677880157517</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
@@ -2437,16 +2437,16 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>141.2296047131211</v>
+        <v>129.0705356387007</v>
       </c>
       <c r="R24" t="n">
         <v>130.7823255942661</v>
       </c>
       <c r="S24" t="n">
-        <v>60.9294716627245</v>
+        <v>60.92947166272451</v>
       </c>
       <c r="T24" t="n">
-        <v>3.352067104306286</v>
+        <v>3.352067104306268</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
@@ -2455,7 +2455,7 @@
         <v>368.0000000000007</v>
       </c>
       <c r="W24" t="n">
-        <v>31.37314290982852</v>
+        <v>368.0000000000007</v>
       </c>
       <c r="X24" t="n">
         <v>368.0000000000007</v>
@@ -2504,7 +2504,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>86.8416441894351</v>
+        <v>86.84164418943513</v>
       </c>
       <c r="N25" t="n">
         <v>138.1747801897177</v>
@@ -2519,7 +2519,7 @@
         <v>307.323266425598</v>
       </c>
       <c r="R25" t="n">
-        <v>316.1966197844298</v>
+        <v>316.1966197844297</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -2550,10 +2550,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0</v>
+        <v>172.9993129555745</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>140.4745782429939</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
@@ -2562,13 +2562,13 @@
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>95.88962870801186</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>94.23383960805002</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -2607,19 +2607,19 @@
         <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>326</v>
+        <v>152.2616070246841</v>
       </c>
       <c r="V26" t="n">
-        <v>127.5415338565257</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>326</v>
+        <v>326.0000000000177</v>
       </c>
       <c r="X26" t="n">
         <v>283.2818334606677</v>
       </c>
       <c r="Y26" t="n">
-        <v>202.3174326828064</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -2738,7 +2738,7 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>83.4482183217136</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -2747,19 +2747,19 @@
         <v>230.1747801897177</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>7.237982730280275</v>
       </c>
       <c r="P28" t="n">
-        <v>326</v>
+        <v>326.0000000000348</v>
       </c>
       <c r="Q28" t="n">
-        <v>299.5178014885686</v>
+        <v>326.000000000031</v>
       </c>
       <c r="R28" t="n">
-        <v>326</v>
+        <v>326.0000000000317</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>49.72803707990462</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
@@ -2796,7 +2796,7 @@
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>58.24105199399634</v>
+        <v>95.36328960686865</v>
       </c>
       <c r="F29" t="n">
         <v>95.88962870801186</v>
@@ -2805,7 +2805,7 @@
         <v>94.29104062872476</v>
       </c>
       <c r="H29" t="n">
-        <v>94.23383960805002</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -2841,7 +2841,7 @@
         <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>275.634214894393</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
         <v>326</v>
@@ -2850,10 +2850,10 @@
         <v>320.8510241668239</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>326</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>6.745816889570741</v>
       </c>
       <c r="Y29" t="n">
         <v>0</v>
@@ -2887,7 +2887,7 @@
         <v>20.75835133736453</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>4.59417533221779</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2911,7 +2911,7 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>4.594175332217801</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
         <v>222.7823255942661</v>
@@ -2984,19 +2984,19 @@
         <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>301.8788755544248</v>
+        <v>237.4127629200954</v>
       </c>
       <c r="P31" t="n">
         <v>326</v>
       </c>
       <c r="Q31" t="n">
-        <v>311.2619244455752</v>
+        <v>326</v>
       </c>
       <c r="R31" t="n">
         <v>326</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>49.72803707990462</v>
       </c>
       <c r="T31" t="n">
         <v>0</v>
@@ -3072,10 +3072,10 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>1.425702460839329</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>57.22163513900632</v>
+        <v>58.64733759984559</v>
       </c>
       <c r="T32" t="n">
         <v>157.634214894393</v>
@@ -3106,7 +3106,7 @@
         <v>0</v>
       </c>
       <c r="C33" t="n">
-        <v>223.515582889393</v>
+        <v>0</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
@@ -3124,7 +3124,7 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>208.5358198536127</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3148,13 +3148,13 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>141.2296047131211</v>
       </c>
       <c r="R33" t="n">
-        <v>104.7823255942661</v>
+        <v>304.0000000000019</v>
       </c>
       <c r="S33" t="n">
-        <v>34.92947166272451</v>
+        <v>304.0000000000019</v>
       </c>
       <c r="T33" t="n">
         <v>304.0000000000019</v>
@@ -3166,10 +3166,10 @@
         <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>304.0000000000019</v>
+        <v>5.373142909828516</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>121.1604523770447</v>
       </c>
       <c r="Y33" t="n">
         <v>0</v>
@@ -3312,25 +3312,25 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>52.22163513900631</v>
+        <v>52.22163513900632</v>
       </c>
       <c r="T35" t="n">
         <v>152.634214894393</v>
       </c>
       <c r="U35" t="n">
-        <v>217.1839900159473</v>
+        <v>217.1839900159474</v>
       </c>
       <c r="V35" t="n">
         <v>197.8510241668239</v>
       </c>
       <c r="W35" t="n">
-        <v>206.2295784417869</v>
+        <v>206.3734759809475</v>
       </c>
       <c r="X35" t="n">
         <v>160.2818334606677</v>
       </c>
       <c r="Y35" t="n">
-        <v>79.31743268280638</v>
+        <v>79.17353514364562</v>
       </c>
     </row>
     <row r="36">
@@ -3343,16 +3343,16 @@
         <v>0</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>277.8790551200448</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>292.0000000000074</v>
       </c>
       <c r="E36" t="n">
-        <v>292</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>292</v>
+        <v>292.0000000000074</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -3388,10 +3388,10 @@
         <v>141.2296047131211</v>
       </c>
       <c r="R36" t="n">
-        <v>99.78232559426613</v>
+        <v>99.78232559426608</v>
       </c>
       <c r="S36" t="n">
-        <v>29.9294716627245</v>
+        <v>29.92947166272451</v>
       </c>
       <c r="T36" t="n">
         <v>0</v>
@@ -3406,7 +3406,7 @@
         <v>0.3731429098285162</v>
       </c>
       <c r="X36" t="n">
-        <v>277.8790551200597</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
         <v>0</v>
@@ -3452,13 +3452,13 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>55.8416441894351</v>
+        <v>55.47157055361782</v>
       </c>
       <c r="N37" t="n">
         <v>107.1747801897177</v>
       </c>
       <c r="O37" t="n">
-        <v>178.5088019186073</v>
+        <v>178.8788755544248</v>
       </c>
       <c r="P37" t="n">
         <v>230.1484874922119</v>
@@ -3467,7 +3467,7 @@
         <v>276.323266425598</v>
       </c>
       <c r="R37" t="n">
-        <v>285.1966197844298</v>
+        <v>285.1966197844297</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -3549,19 +3549,19 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>52.22163513900631</v>
+        <v>52.07773759984563</v>
       </c>
       <c r="T38" t="n">
         <v>152.634214894393</v>
       </c>
       <c r="U38" t="n">
-        <v>217.1839900159473</v>
+        <v>217.1839900159474</v>
       </c>
       <c r="V38" t="n">
         <v>197.8510241668239</v>
       </c>
       <c r="W38" t="n">
-        <v>206.2295784417869</v>
+        <v>206.3734759809475</v>
       </c>
       <c r="X38" t="n">
         <v>160.2818334606677</v>
@@ -3580,16 +3580,16 @@
         <v>0</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>277.8790551200305</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>292.0000000000146</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>292.0000000000146</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -3622,28 +3622,28 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>141.2296047131211</v>
       </c>
       <c r="R39" t="n">
-        <v>99.78232559426613</v>
+        <v>99.78232559426608</v>
       </c>
       <c r="S39" t="n">
-        <v>29.9294716627245</v>
+        <v>29.92947166272451</v>
       </c>
       <c r="T39" t="n">
         <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>292</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>292</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>292</v>
+        <v>0.3731429098285162</v>
       </c>
       <c r="X39" t="n">
-        <v>127.4818027430092</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
         <v>0</v>
@@ -3689,13 +3689,13 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>55.8416441894351</v>
+        <v>55.47157055361782</v>
       </c>
       <c r="N40" t="n">
         <v>107.1747801897177</v>
       </c>
       <c r="O40" t="n">
-        <v>178.5088019186073</v>
+        <v>178.8788755544248</v>
       </c>
       <c r="P40" t="n">
         <v>230.1484874922119</v>
@@ -3704,7 +3704,7 @@
         <v>276.323266425598</v>
       </c>
       <c r="R40" t="n">
-        <v>285.1966197844298</v>
+        <v>285.1966197844297</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -3735,22 +3735,22 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0</v>
+        <v>164.9993129555745</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>132.4745782429939</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>93.33915573984979</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>87.36328960686865</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>87.88962870801186</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>86.29104062872476</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -3789,22 +3789,22 @@
         <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>267.634214894393</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>281.5593851056069</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>292</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>292</v>
+        <v>11.23732797450218</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>275.2818334606677</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>194.3174326828064</v>
       </c>
     </row>
     <row r="42">
@@ -3923,7 +3923,7 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>75.4482183217136</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
@@ -3932,19 +3932,19 @@
         <v>222.1747801897177</v>
       </c>
       <c r="O43" t="n">
-        <v>292</v>
+        <v>292.0000000002563</v>
       </c>
       <c r="P43" t="n">
-        <v>292</v>
+        <v>292.0000000002629</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>251.5706014880495</v>
       </c>
       <c r="R43" t="n">
-        <v>285.2907827303775</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>41.72803707990462</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
@@ -3972,25 +3972,25 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>208.9993129555745</v>
+        <v>76.31763462529089</v>
       </c>
       <c r="C44" t="n">
-        <v>176.4745782429939</v>
+        <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>137.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E44" t="n">
         <v>131.3632896068686</v>
       </c>
       <c r="F44" t="n">
-        <v>131.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>130.2910406287248</v>
+        <v>130.2910406287247</v>
       </c>
       <c r="H44" t="n">
-        <v>130.23383960805</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -4023,25 +4023,25 @@
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>211.2216351390063</v>
       </c>
       <c r="T44" t="n">
         <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>292.0000000000546</v>
       </c>
       <c r="V44" t="n">
         <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>292.0000000000546</v>
       </c>
       <c r="X44" t="n">
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>86.6027545099264</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -4051,25 +4051,25 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>111.5565566463266</v>
+        <v>0</v>
       </c>
       <c r="C45" t="n">
         <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>74.93768689770263</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>69.67209722191262</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>66.63624233787687</v>
       </c>
       <c r="G45" t="n">
         <v>52.49002644106508</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>56.75835133736453</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
@@ -4099,10 +4099,10 @@
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>106.9067340766881</v>
+        <v>139.3883845908827</v>
       </c>
       <c r="S45" t="n">
-        <v>188.9294716627245</v>
+        <v>0</v>
       </c>
       <c r="T45" t="n">
         <v>131.3520671043063</v>
@@ -4169,10 +4169,10 @@
         <v>266.1747801897177</v>
       </c>
       <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="n">
         <v>105.5312905597693</v>
-      </c>
-      <c r="P46" t="n">
-        <v>0</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -4297,7 +4297,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>77.03690301297344</v>
+        <v>68.46100369637152</v>
       </c>
       <c r="C2" t="n">
         <v>32.11308660590888</v>
@@ -4321,25 +4321,25 @@
         <v>26.72</v>
       </c>
       <c r="J2" t="n">
-        <v>357.38</v>
+        <v>31.210947234446</v>
       </c>
       <c r="K2" t="n">
-        <v>416.105944321608</v>
+        <v>89.93689155605404</v>
       </c>
       <c r="L2" t="n">
-        <v>488.9606711557789</v>
+        <v>162.7916183902249</v>
       </c>
       <c r="M2" t="n">
-        <v>819.620671155779</v>
+        <v>493.4516183902249</v>
       </c>
       <c r="N2" t="n">
-        <v>1150.280671155779</v>
+        <v>824.111618390225</v>
       </c>
       <c r="O2" t="n">
-        <v>1158.521202086473</v>
+        <v>1154.771618390225</v>
       </c>
       <c r="P2" t="n">
-        <v>1224.625497269314</v>
+        <v>1220.875913573066</v>
       </c>
       <c r="Q2" t="n">
         <v>1336</v>
@@ -4363,10 +4363,10 @@
         <v>365.02591899281</v>
       </c>
       <c r="X2" t="n">
-        <v>262.2053329507319</v>
+        <v>175.8523498406204</v>
       </c>
       <c r="Y2" t="n">
-        <v>154.8139868064831</v>
+        <v>68.46100369637152</v>
       </c>
     </row>
     <row r="3">
@@ -4376,25 +4376,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>364.0937373737374</v>
+        <v>237.3622422763765</v>
       </c>
       <c r="C3" t="n">
-        <v>364.0937373737374</v>
+        <v>237.3622422763765</v>
       </c>
       <c r="D3" t="n">
-        <v>364.0937373737374</v>
+        <v>237.3622422763765</v>
       </c>
       <c r="E3" t="n">
-        <v>364.0937373737374</v>
+        <v>237.3622422763765</v>
       </c>
       <c r="F3" t="n">
-        <v>26.72</v>
+        <v>237.3622422763765</v>
       </c>
       <c r="G3" t="n">
-        <v>26.72</v>
+        <v>237.3622422763765</v>
       </c>
       <c r="H3" t="n">
-        <v>26.72</v>
+        <v>237.3622422763765</v>
       </c>
       <c r="I3" t="n">
         <v>26.72</v>
@@ -4403,49 +4403,49 @@
         <v>174.0139582885065</v>
       </c>
       <c r="K3" t="n">
-        <v>367.009622257446</v>
+        <v>403.0941732508144</v>
       </c>
       <c r="L3" t="n">
-        <v>691.9936140413254</v>
+        <v>532.2953646661583</v>
       </c>
       <c r="M3" t="n">
-        <v>840.6619557841846</v>
+        <v>680.9637064090175</v>
       </c>
       <c r="N3" t="n">
-        <v>1038.186553221941</v>
+        <v>878.4883038467744</v>
       </c>
       <c r="O3" t="n">
-        <v>1336</v>
+        <v>1176.301750624833</v>
       </c>
       <c r="P3" t="n">
         <v>1336</v>
       </c>
       <c r="Q3" t="n">
-        <v>1234.01541863486</v>
+        <v>1193.34383362311</v>
       </c>
       <c r="R3" t="n">
-        <v>1105.952463489136</v>
+        <v>855.9700962493725</v>
       </c>
       <c r="S3" t="n">
-        <v>1048.447946658101</v>
+        <v>518.5963588756351</v>
       </c>
       <c r="T3" t="n">
-        <v>1048.447946658101</v>
+        <v>518.5963588756351</v>
       </c>
       <c r="U3" t="n">
-        <v>1048.447946658101</v>
+        <v>518.5963588756351</v>
       </c>
       <c r="V3" t="n">
-        <v>1038.841212121212</v>
+        <v>508.9896243387461</v>
       </c>
       <c r="W3" t="n">
-        <v>701.4674747474749</v>
+        <v>481.339985035889</v>
       </c>
       <c r="X3" t="n">
-        <v>364.0937373737374</v>
+        <v>237.3622422763765</v>
       </c>
       <c r="Y3" t="n">
-        <v>364.0937373737374</v>
+        <v>237.3622422763765</v>
       </c>
     </row>
     <row r="4">
@@ -4455,7 +4455,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>189.2365809571866</v>
+        <v>115.0764890589139</v>
       </c>
       <c r="C4" t="n">
         <v>246.0284948773497</v>
@@ -4564,19 +4564,19 @@
         <v>89.93689155605404</v>
       </c>
       <c r="L5" t="n">
-        <v>269.6751738864651</v>
+        <v>162.7916183902249</v>
       </c>
       <c r="M5" t="n">
-        <v>600.3351738864651</v>
+        <v>493.4516183902249</v>
       </c>
       <c r="N5" t="n">
-        <v>930.9951738864652</v>
+        <v>824.111618390225</v>
       </c>
       <c r="O5" t="n">
-        <v>939.2357048171589</v>
+        <v>1005.34</v>
       </c>
       <c r="P5" t="n">
-        <v>1005.34</v>
+        <v>1336</v>
       </c>
       <c r="Q5" t="n">
         <v>1336</v>
@@ -4585,7 +4585,7 @@
         <v>1336</v>
       </c>
       <c r="S5" t="n">
-        <v>1255.978146324236</v>
+        <v>1336</v>
       </c>
       <c r="T5" t="n">
         <v>1160.882427520819</v>
@@ -4613,19 +4613,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>237.3622422763765</v>
+        <v>566.1400467623008</v>
       </c>
       <c r="C6" t="n">
-        <v>237.3622422763765</v>
+        <v>566.1400467623008</v>
       </c>
       <c r="D6" t="n">
-        <v>237.3622422763765</v>
+        <v>566.1400467623008</v>
       </c>
       <c r="E6" t="n">
-        <v>237.3622422763765</v>
+        <v>566.1400467623008</v>
       </c>
       <c r="F6" t="n">
-        <v>237.3622422763765</v>
+        <v>566.1400467623008</v>
       </c>
       <c r="G6" t="n">
         <v>237.3622422763765</v>
@@ -4643,16 +4643,16 @@
         <v>403.0941732508144</v>
       </c>
       <c r="L6" t="n">
-        <v>532.2953646661583</v>
+        <v>691.9936140413254</v>
       </c>
       <c r="M6" t="n">
-        <v>680.9637064090175</v>
+        <v>840.6619557841846</v>
       </c>
       <c r="N6" t="n">
-        <v>878.4883038467744</v>
+        <v>1038.186553221941</v>
       </c>
       <c r="O6" t="n">
-        <v>1176.301750624833</v>
+        <v>1336</v>
       </c>
       <c r="P6" t="n">
         <v>1336</v>
@@ -4664,25 +4664,25 @@
         <v>855.9700962493725</v>
       </c>
       <c r="S6" t="n">
-        <v>518.5963588756351</v>
+        <v>618.409288728701</v>
       </c>
       <c r="T6" t="n">
-        <v>518.5963588756351</v>
+        <v>618.409288728701</v>
       </c>
       <c r="U6" t="n">
-        <v>518.5963588756351</v>
+        <v>618.409288728701</v>
       </c>
       <c r="V6" t="n">
-        <v>508.9896243387461</v>
+        <v>608.802554191812</v>
       </c>
       <c r="W6" t="n">
-        <v>252.3751104030306</v>
+        <v>581.1529148889549</v>
       </c>
       <c r="X6" t="n">
-        <v>237.3622422763765</v>
+        <v>566.1400467623008</v>
       </c>
       <c r="Y6" t="n">
-        <v>237.3622422763765</v>
+        <v>566.1400467623008</v>
       </c>
     </row>
     <row r="7">
@@ -4692,34 +4692,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>796.3797405151413</v>
+        <v>26.72</v>
       </c>
       <c r="C7" t="n">
-        <v>927.331746333577</v>
+        <v>26.72</v>
       </c>
       <c r="D7" t="n">
-        <v>1045.600890458577</v>
+        <v>144.9891441250001</v>
       </c>
       <c r="E7" t="n">
-        <v>1168.37979466999</v>
+        <v>267.7680483364131</v>
       </c>
       <c r="F7" t="n">
-        <v>1297.690767261926</v>
+        <v>397.0790209283485</v>
       </c>
       <c r="G7" t="n">
-        <v>1335.370175389715</v>
+        <v>555.642675339824</v>
       </c>
       <c r="H7" t="n">
-        <v>1335.370175389715</v>
+        <v>731.9504657451232</v>
       </c>
       <c r="I7" t="n">
-        <v>1335.370175389715</v>
+        <v>964.2610614025176</v>
       </c>
       <c r="J7" t="n">
-        <v>1335.370175389715</v>
+        <v>1294.921061402518</v>
       </c>
       <c r="K7" t="n">
-        <v>1335.370175389715</v>
+        <v>1322.943911528211</v>
       </c>
       <c r="L7" t="n">
         <v>1335.370175389715</v>
@@ -4752,16 +4752,16 @@
         <v>26.72</v>
       </c>
       <c r="V7" t="n">
-        <v>230.491392885946</v>
+        <v>26.72</v>
       </c>
       <c r="W7" t="n">
-        <v>407.3323111456234</v>
+        <v>26.72</v>
       </c>
       <c r="X7" t="n">
-        <v>563.3131021698169</v>
+        <v>26.72</v>
       </c>
       <c r="Y7" t="n">
-        <v>679.6724028488492</v>
+        <v>26.72</v>
       </c>
     </row>
     <row r="8">
@@ -4801,19 +4801,19 @@
         <v>91.69689155605403</v>
       </c>
       <c r="L8" t="n">
-        <v>292.3351738864637</v>
+        <v>292.3351738864652</v>
       </c>
       <c r="M8" t="n">
-        <v>644.7751738864642</v>
+        <v>644.7751738864652</v>
       </c>
       <c r="N8" t="n">
-        <v>997.2151738864648</v>
+        <v>997.2151738864652</v>
       </c>
       <c r="O8" t="n">
-        <v>1005.455704817158</v>
+        <v>1005.455704817159</v>
       </c>
       <c r="P8" t="n">
-        <v>1071.559999999999</v>
+        <v>1071.56</v>
       </c>
       <c r="Q8" t="n">
         <v>1424</v>
@@ -4850,13 +4850,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>374.6134315372855</v>
+        <v>739.5281685835381</v>
       </c>
       <c r="C9" t="n">
-        <v>374.6134315372855</v>
+        <v>379.9322089875785</v>
       </c>
       <c r="D9" t="n">
-        <v>374.6134315372855</v>
+        <v>28.48</v>
       </c>
       <c r="E9" t="n">
         <v>28.48</v>
@@ -4880,16 +4880,16 @@
         <v>404.8541732508144</v>
       </c>
       <c r="L9" t="n">
-        <v>620.2953646661583</v>
+        <v>729.8381650346938</v>
       </c>
       <c r="M9" t="n">
-        <v>768.9637064090175</v>
+        <v>878.506506777553</v>
       </c>
       <c r="N9" t="n">
-        <v>966.4883038467744</v>
+        <v>1076.03110421531</v>
       </c>
       <c r="O9" t="n">
-        <v>1264.301750624833</v>
+        <v>1373.844550993369</v>
       </c>
       <c r="P9" t="n">
         <v>1424</v>
@@ -4916,10 +4916,10 @@
         <v>1058.519987806606</v>
       </c>
       <c r="X9" t="n">
-        <v>734.2093911332452</v>
+        <v>739.5281685835381</v>
       </c>
       <c r="Y9" t="n">
-        <v>734.2093911332452</v>
+        <v>739.5281685835381</v>
       </c>
     </row>
     <row r="10">
@@ -4929,28 +4929,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>28.48</v>
+        <v>835.8191486429301</v>
       </c>
       <c r="C10" t="n">
-        <v>159.4320058184358</v>
+        <v>966.7711544613659</v>
       </c>
       <c r="D10" t="n">
-        <v>277.7011499434358</v>
+        <v>1085.040298586366</v>
       </c>
       <c r="E10" t="n">
-        <v>400.4800541548489</v>
+        <v>1207.819202797779</v>
       </c>
       <c r="F10" t="n">
-        <v>529.7910267467844</v>
+        <v>1337.130175389714</v>
       </c>
       <c r="G10" t="n">
-        <v>688.3546811582598</v>
+        <v>1337.130175389714</v>
       </c>
       <c r="H10" t="n">
-        <v>864.6624715635591</v>
+        <v>1337.130175389714</v>
       </c>
       <c r="I10" t="n">
-        <v>1096.973067220953</v>
+        <v>1337.130175389714</v>
       </c>
       <c r="J10" t="n">
         <v>1337.130175389714</v>
@@ -4986,19 +4986,19 @@
         <v>28.48</v>
       </c>
       <c r="U10" t="n">
-        <v>28.48</v>
+        <v>66.15940812778885</v>
       </c>
       <c r="V10" t="n">
-        <v>28.48</v>
+        <v>269.9308010137348</v>
       </c>
       <c r="W10" t="n">
-        <v>28.48</v>
+        <v>446.7717192734123</v>
       </c>
       <c r="X10" t="n">
-        <v>28.48</v>
+        <v>602.7525102976058</v>
       </c>
       <c r="Y10" t="n">
-        <v>28.48</v>
+        <v>719.111810976638</v>
       </c>
     </row>
     <row r="11">
@@ -5008,22 +5008,22 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>426.4770225229538</v>
+        <v>596.7041742772717</v>
       </c>
       <c r="C11" t="n">
-        <v>294.6845192472023</v>
+        <v>464.9116710015203</v>
       </c>
       <c r="D11" t="n">
-        <v>202.4227457726066</v>
+        <v>372.6498975269245</v>
       </c>
       <c r="E11" t="n">
-        <v>116.1972007151635</v>
+        <v>286.4243524694814</v>
       </c>
       <c r="F11" t="n">
-        <v>29.44</v>
+        <v>199.667151754318</v>
       </c>
       <c r="G11" t="n">
-        <v>29.44</v>
+        <v>114.5246864727778</v>
       </c>
       <c r="H11" t="n">
         <v>29.44</v>
@@ -5032,25 +5032,25 @@
         <v>29.44</v>
       </c>
       <c r="J11" t="n">
-        <v>33.93094723444601</v>
+        <v>393.76</v>
       </c>
       <c r="K11" t="n">
-        <v>92.65689155605405</v>
+        <v>452.485944321608</v>
       </c>
       <c r="L11" t="n">
-        <v>304.6951738864632</v>
+        <v>525.3406711557789</v>
       </c>
       <c r="M11" t="n">
-        <v>669.0151738864639</v>
+        <v>889.6606711557788</v>
       </c>
       <c r="N11" t="n">
-        <v>1033.335173886465</v>
+        <v>1253.980671155779</v>
       </c>
       <c r="O11" t="n">
-        <v>1041.575704817158</v>
+        <v>1262.221202086472</v>
       </c>
       <c r="P11" t="n">
-        <v>1107.679999999999</v>
+        <v>1328.325497269313</v>
       </c>
       <c r="Q11" t="n">
         <v>1472</v>
@@ -5059,25 +5059,25 @@
         <v>1472</v>
       </c>
       <c r="S11" t="n">
-        <v>1305.109459455549</v>
+        <v>1472</v>
       </c>
       <c r="T11" t="n">
-        <v>1305.109459455549</v>
+        <v>1472</v>
       </c>
       <c r="U11" t="n">
-        <v>1305.109459455549</v>
+        <v>1472</v>
       </c>
       <c r="V11" t="n">
-        <v>1305.109459455549</v>
+        <v>1195.345900985974</v>
       </c>
       <c r="W11" t="n">
-        <v>1061.425082218962</v>
+        <v>872.7464302981482</v>
       </c>
       <c r="X11" t="n">
-        <v>785.382826198086</v>
+        <v>596.7041742772717</v>
       </c>
       <c r="Y11" t="n">
-        <v>591.1227931851503</v>
+        <v>596.7041742772717</v>
       </c>
     </row>
     <row r="12">
@@ -5087,25 +5087,25 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>163.3736532135768</v>
+        <v>341.5132194954925</v>
       </c>
       <c r="C12" t="n">
-        <v>120.8484891271937</v>
+        <v>298.9880554091093</v>
       </c>
       <c r="D12" t="n">
-        <v>91.61850236183749</v>
+        <v>269.7580686437531</v>
       </c>
       <c r="E12" t="n">
-        <v>67.70729304677423</v>
+        <v>245.8468593286899</v>
       </c>
       <c r="F12" t="n">
-        <v>46.86260381659557</v>
+        <v>225.0021700985112</v>
       </c>
       <c r="G12" t="n">
-        <v>40.30702155289347</v>
+        <v>218.4465878348091</v>
       </c>
       <c r="H12" t="n">
-        <v>29.44</v>
+        <v>207.5795662819156</v>
       </c>
       <c r="I12" t="n">
         <v>29.44</v>
@@ -5117,13 +5117,13 @@
         <v>405.8141732508144</v>
       </c>
       <c r="L12" t="n">
-        <v>730.7981650346937</v>
+        <v>668.2953646661583</v>
       </c>
       <c r="M12" t="n">
-        <v>879.4665067775529</v>
+        <v>816.9637064090175</v>
       </c>
       <c r="N12" t="n">
-        <v>1076.99110421531</v>
+        <v>1014.488303846774</v>
       </c>
       <c r="O12" t="n">
         <v>1312.301750624833</v>
@@ -5147,16 +5147,16 @@
         <v>801.8106931916514</v>
       </c>
       <c r="V12" t="n">
-        <v>527.1957055041597</v>
+        <v>705.3352717860754</v>
       </c>
       <c r="W12" t="n">
-        <v>412.6773793326157</v>
+        <v>590.8169456145314</v>
       </c>
       <c r="X12" t="n">
-        <v>310.7958243372748</v>
+        <v>488.9353906191905</v>
       </c>
       <c r="Y12" t="n">
-        <v>229.5923973007754</v>
+        <v>407.7319635826911</v>
       </c>
     </row>
     <row r="13">
@@ -5196,16 +5196,16 @@
         <v>1470.825062647096</v>
       </c>
       <c r="L13" t="n">
-        <v>1470.825062647096</v>
+        <v>1396.634943130214</v>
       </c>
       <c r="M13" t="n">
-        <v>1300.277947304232</v>
+        <v>1226.08782778735</v>
       </c>
       <c r="N13" t="n">
-        <v>1077.879179435831</v>
+        <v>1119.488977264861</v>
       </c>
       <c r="O13" t="n">
-        <v>783.0520324111591</v>
+        <v>1119.488977264861</v>
       </c>
       <c r="P13" t="n">
         <v>772.8743434343435</v>
@@ -5245,22 +5245,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>330.0375076106051</v>
+        <v>29.44</v>
       </c>
       <c r="C14" t="n">
-        <v>242.6894487792981</v>
+        <v>29.44</v>
       </c>
       <c r="D14" t="n">
-        <v>194.8721197491468</v>
+        <v>29.44</v>
       </c>
       <c r="E14" t="n">
-        <v>153.0910191361481</v>
+        <v>29.44</v>
       </c>
       <c r="F14" t="n">
-        <v>110.7782628654291</v>
+        <v>29.44</v>
       </c>
       <c r="G14" t="n">
-        <v>70.08024202833336</v>
+        <v>29.44</v>
       </c>
       <c r="H14" t="n">
         <v>29.44</v>
@@ -5269,25 +5269,25 @@
         <v>29.44</v>
       </c>
       <c r="J14" t="n">
-        <v>393.7600000000007</v>
+        <v>33.93094723444601</v>
       </c>
       <c r="K14" t="n">
-        <v>452.4859443216088</v>
+        <v>92.65689155605405</v>
       </c>
       <c r="L14" t="n">
-        <v>525.3406711557797</v>
+        <v>304.6951738864654</v>
       </c>
       <c r="M14" t="n">
-        <v>669.0151738864639</v>
+        <v>669.0151738864654</v>
       </c>
       <c r="N14" t="n">
         <v>1033.335173886465</v>
       </c>
       <c r="O14" t="n">
-        <v>1041.575704817158</v>
+        <v>1041.575704817159</v>
       </c>
       <c r="P14" t="n">
-        <v>1107.679999999999</v>
+        <v>1107.68</v>
       </c>
       <c r="Q14" t="n">
         <v>1472</v>
@@ -5296,25 +5296,25 @@
         <v>1472</v>
       </c>
       <c r="S14" t="n">
-        <v>1472</v>
+        <v>1349.553903899994</v>
       </c>
       <c r="T14" t="n">
-        <v>1472</v>
+        <v>1125.680959562223</v>
       </c>
       <c r="U14" t="n">
-        <v>1182.925262610154</v>
+        <v>836.6062221723771</v>
       </c>
       <c r="V14" t="n">
-        <v>1109.807260216662</v>
+        <v>567.0597331149793</v>
       </c>
       <c r="W14" t="n">
-        <v>831.6522339732804</v>
+        <v>288.9047068715979</v>
       </c>
       <c r="X14" t="n">
-        <v>600.0544223968484</v>
+        <v>179.2555885684913</v>
       </c>
       <c r="Y14" t="n">
-        <v>450.2388338283571</v>
+        <v>29.44</v>
       </c>
     </row>
     <row r="15">
@@ -5324,7 +5324,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>47.14859109454582</v>
+        <v>29.44</v>
       </c>
       <c r="C15" t="n">
         <v>29.44</v>
@@ -5363,7 +5363,7 @@
         <v>1076.99110421531</v>
       </c>
       <c r="O15" t="n">
-        <v>1312.301750624833</v>
+        <v>1374.804550993368</v>
       </c>
       <c r="P15" t="n">
         <v>1472</v>
@@ -5372,28 +5372,28 @@
         <v>1472</v>
       </c>
       <c r="R15" t="n">
-        <v>1100.282828282828</v>
+        <v>1301.512802430034</v>
       </c>
       <c r="S15" t="n">
-        <v>1000.354069027551</v>
+        <v>1201.584043174757</v>
       </c>
       <c r="T15" t="n">
-        <v>958.5843042757264</v>
+        <v>1159.814278422932</v>
       </c>
       <c r="U15" t="n">
-        <v>586.8671325585547</v>
+        <v>916.7535017653287</v>
       </c>
       <c r="V15" t="n">
-        <v>534.8361555974232</v>
+        <v>864.7225248041972</v>
       </c>
       <c r="W15" t="n">
-        <v>163.1189838802514</v>
+        <v>794.6486430770976</v>
       </c>
       <c r="X15" t="n">
-        <v>105.6818733293549</v>
+        <v>422.9314713599259</v>
       </c>
       <c r="Y15" t="n">
-        <v>68.92289073729998</v>
+        <v>51.21429964275416</v>
       </c>
     </row>
     <row r="16">
@@ -5403,76 +5403,76 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>795.5005912417714</v>
+        <v>957.6919841277174</v>
       </c>
       <c r="C16" t="n">
-        <v>884.8725970602072</v>
+        <v>1047.063989946153</v>
       </c>
       <c r="D16" t="n">
-        <v>961.5617411852073</v>
+        <v>1123.753134071153</v>
       </c>
       <c r="E16" t="n">
-        <v>1042.76064539662</v>
+        <v>1204.952038282566</v>
       </c>
       <c r="F16" t="n">
-        <v>1130.491617988556</v>
+        <v>1292.683010874502</v>
       </c>
       <c r="G16" t="n">
-        <v>1247.475272400031</v>
+        <v>1409.666665285977</v>
       </c>
       <c r="H16" t="n">
-        <v>1382.203062805331</v>
+        <v>1472</v>
       </c>
       <c r="I16" t="n">
-        <v>1382.203062805331</v>
+        <v>1472</v>
       </c>
       <c r="J16" t="n">
-        <v>1382.203062805331</v>
+        <v>1472</v>
       </c>
       <c r="K16" t="n">
         <v>1472</v>
       </c>
       <c r="L16" t="n">
-        <v>1442.254324927562</v>
+        <v>1472</v>
       </c>
       <c r="M16" t="n">
-        <v>1316.151654029143</v>
+        <v>1345.897329101581</v>
       </c>
       <c r="N16" t="n">
-        <v>1138.197330605185</v>
+        <v>1167.943005677623</v>
       </c>
       <c r="O16" t="n">
-        <v>887.8146280249584</v>
+        <v>917.5603030973964</v>
       </c>
       <c r="P16" t="n">
-        <v>585.6444386388857</v>
+        <v>615.3901137113238</v>
       </c>
       <c r="Q16" t="n">
-        <v>236.8330584110089</v>
+        <v>387.214363418616</v>
       </c>
       <c r="R16" t="n">
         <v>29.44</v>
       </c>
       <c r="S16" t="n">
-        <v>33.66924329089443</v>
+        <v>33.66924329089445</v>
       </c>
       <c r="T16" t="n">
-        <v>185.9997552365845</v>
+        <v>185.9997552365846</v>
       </c>
       <c r="U16" t="n">
         <v>395.9322436125761</v>
       </c>
       <c r="V16" t="n">
-        <v>395.9322436125761</v>
+        <v>558.123636498522</v>
       </c>
       <c r="W16" t="n">
-        <v>531.1931618722535</v>
+        <v>693.3845547581994</v>
       </c>
       <c r="X16" t="n">
-        <v>645.593952896447</v>
+        <v>807.7853457823929</v>
       </c>
       <c r="Y16" t="n">
-        <v>720.3732535754793</v>
+        <v>882.5646464614252</v>
       </c>
     </row>
     <row r="17">
@@ -5506,25 +5506,25 @@
         <v>29.44</v>
       </c>
       <c r="J17" t="n">
-        <v>393.7600000000007</v>
+        <v>33.93094723444601</v>
       </c>
       <c r="K17" t="n">
-        <v>452.4859443216088</v>
+        <v>92.65689155605405</v>
       </c>
       <c r="L17" t="n">
-        <v>525.3406711557797</v>
+        <v>304.6951738864654</v>
       </c>
       <c r="M17" t="n">
-        <v>889.6606711557804</v>
+        <v>669.0151738864654</v>
       </c>
       <c r="N17" t="n">
-        <v>1253.980671155781</v>
+        <v>1033.335173886465</v>
       </c>
       <c r="O17" t="n">
-        <v>1262.221202086475</v>
+        <v>1041.575704817159</v>
       </c>
       <c r="P17" t="n">
-        <v>1328.325497269316</v>
+        <v>1107.68</v>
       </c>
       <c r="Q17" t="n">
         <v>1472</v>
@@ -5533,16 +5533,16 @@
         <v>1472</v>
       </c>
       <c r="S17" t="n">
-        <v>1387.937742283832</v>
+        <v>1393.311532011777</v>
       </c>
       <c r="T17" t="n">
-        <v>1202.4486363299</v>
+        <v>1207.822426057845</v>
       </c>
       <c r="U17" t="n">
-        <v>951.7577373238923</v>
+        <v>957.1315270518375</v>
       </c>
       <c r="V17" t="n">
-        <v>720.5950866503329</v>
+        <v>725.968876378278</v>
       </c>
       <c r="W17" t="n">
         <v>486.1976885187349</v>
@@ -5561,22 +5561,22 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>29.44</v>
+        <v>362.5292437751157</v>
       </c>
       <c r="C18" t="n">
-        <v>29.44</v>
+        <v>362.5292437751157</v>
       </c>
       <c r="D18" t="n">
-        <v>29.44</v>
+        <v>362.5292437751157</v>
       </c>
       <c r="E18" t="n">
-        <v>29.44</v>
+        <v>362.5292437751157</v>
       </c>
       <c r="F18" t="n">
-        <v>29.44</v>
+        <v>362.5292437751157</v>
       </c>
       <c r="G18" t="n">
-        <v>29.44</v>
+        <v>362.5292437751157</v>
       </c>
       <c r="H18" t="n">
         <v>29.44</v>
@@ -5600,7 +5600,7 @@
         <v>1076.99110421531</v>
       </c>
       <c r="O18" t="n">
-        <v>1374.804550993368</v>
+        <v>1312.301750624833</v>
       </c>
       <c r="P18" t="n">
         <v>1472</v>
@@ -5609,28 +5609,28 @@
         <v>1329.34383362311</v>
       </c>
       <c r="R18" t="n">
-        <v>957.6266619059381</v>
+        <v>1197.240474436983</v>
       </c>
       <c r="S18" t="n">
-        <v>585.9094901887663</v>
+        <v>1128.402785744503</v>
       </c>
       <c r="T18" t="n">
-        <v>465.5476258047841</v>
+        <v>1125.016859376517</v>
       </c>
       <c r="U18" t="n">
-        <v>93.83045408761235</v>
+        <v>1125.016859376517</v>
       </c>
       <c r="V18" t="n">
-        <v>80.18331551031926</v>
+        <v>753.2996876593456</v>
       </c>
       <c r="W18" t="n">
-        <v>48.49327216705813</v>
+        <v>381.5825159421738</v>
       </c>
       <c r="X18" t="n">
-        <v>29.44</v>
+        <v>362.5292437751157</v>
       </c>
       <c r="Y18" t="n">
-        <v>29.44</v>
+        <v>362.5292437751157</v>
       </c>
     </row>
     <row r="19">
@@ -5640,34 +5640,34 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>371.4113029698836</v>
+        <v>71.28924329089443</v>
       </c>
       <c r="C19" t="n">
-        <v>371.4113029698836</v>
+        <v>71.28924329089443</v>
       </c>
       <c r="D19" t="n">
-        <v>371.4113029698836</v>
+        <v>71.28924329089443</v>
       </c>
       <c r="E19" t="n">
-        <v>490.2302071812967</v>
+        <v>173.4789674561871</v>
       </c>
       <c r="F19" t="n">
-        <v>490.2302071812967</v>
+        <v>298.8299400481226</v>
       </c>
       <c r="G19" t="n">
-        <v>597.3142135694454</v>
+        <v>453.433594459598</v>
       </c>
       <c r="H19" t="n">
-        <v>769.6620039747446</v>
+        <v>625.7813848648972</v>
       </c>
       <c r="I19" t="n">
-        <v>998.012599632139</v>
+        <v>854.1319805222915</v>
       </c>
       <c r="J19" t="n">
-        <v>1362.332599632139</v>
+        <v>1218.451980522291</v>
       </c>
       <c r="K19" t="n">
-        <v>1362.332599632139</v>
+        <v>1353.866335770635</v>
       </c>
       <c r="L19" t="n">
         <v>1362.332599632139</v>
@@ -5691,25 +5691,25 @@
         <v>29.44</v>
       </c>
       <c r="S19" t="n">
-        <v>29.44</v>
+        <v>71.28924329089443</v>
       </c>
       <c r="T19" t="n">
-        <v>219.3905119456901</v>
+        <v>71.28924329089443</v>
       </c>
       <c r="U19" t="n">
-        <v>219.3905119456901</v>
+        <v>71.28924329089443</v>
       </c>
       <c r="V19" t="n">
-        <v>219.3905119456901</v>
+        <v>71.28924329089443</v>
       </c>
       <c r="W19" t="n">
-        <v>219.3905119456901</v>
+        <v>71.28924329089443</v>
       </c>
       <c r="X19" t="n">
-        <v>371.4113029698836</v>
+        <v>71.28924329089443</v>
       </c>
       <c r="Y19" t="n">
-        <v>371.4113029698836</v>
+        <v>71.28924329089443</v>
       </c>
     </row>
     <row r="20">
@@ -5734,7 +5734,7 @@
         <v>34.0105860977523</v>
       </c>
       <c r="G20" t="n">
-        <v>31.69640364449497</v>
+        <v>31.69640364449496</v>
       </c>
       <c r="H20" t="n">
         <v>29.44</v>
@@ -5743,25 +5743,25 @@
         <v>29.44</v>
       </c>
       <c r="J20" t="n">
-        <v>393.7600000000007</v>
+        <v>393.76</v>
       </c>
       <c r="K20" t="n">
-        <v>452.4859443216088</v>
+        <v>452.485944321608</v>
       </c>
       <c r="L20" t="n">
-        <v>525.3406711557797</v>
+        <v>525.3406711557789</v>
       </c>
       <c r="M20" t="n">
-        <v>669.0151738864639</v>
+        <v>669.0151738864654</v>
       </c>
       <c r="N20" t="n">
         <v>1033.335173886465</v>
       </c>
       <c r="O20" t="n">
-        <v>1041.575704817158</v>
+        <v>1041.575704817159</v>
       </c>
       <c r="P20" t="n">
-        <v>1107.679999999999</v>
+        <v>1107.68</v>
       </c>
       <c r="Q20" t="n">
         <v>1472</v>
@@ -5776,16 +5776,16 @@
         <v>1202.4486363299</v>
       </c>
       <c r="U20" t="n">
-        <v>957.1315270518375</v>
+        <v>951.7577373238923</v>
       </c>
       <c r="V20" t="n">
-        <v>725.968876378278</v>
+        <v>720.5950866503329</v>
       </c>
       <c r="W20" t="n">
-        <v>486.1976885187349</v>
+        <v>480.8238987907898</v>
       </c>
       <c r="X20" t="n">
-        <v>292.9837153261413</v>
+        <v>287.6099255981961</v>
       </c>
       <c r="Y20" t="n">
         <v>181.5519651414884</v>
@@ -5798,7 +5798,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>356.1748730188627</v>
+        <v>394.1873863086054</v>
       </c>
       <c r="C21" t="n">
         <v>29.44</v>
@@ -5828,13 +5828,13 @@
         <v>405.8141732508144</v>
       </c>
       <c r="L21" t="n">
-        <v>668.2953646661583</v>
+        <v>730.7981650346937</v>
       </c>
       <c r="M21" t="n">
-        <v>816.9637064090175</v>
+        <v>879.4665067775529</v>
       </c>
       <c r="N21" t="n">
-        <v>1014.488303846774</v>
+        <v>1076.99110421531</v>
       </c>
       <c r="O21" t="n">
         <v>1312.301750624833</v>
@@ -5852,22 +5852,22 @@
         <v>1135.695553565544</v>
       </c>
       <c r="T21" t="n">
-        <v>1132.309627197558</v>
+        <v>1132.309627197557</v>
       </c>
       <c r="U21" t="n">
-        <v>1132.309627197558</v>
+        <v>1132.309627197557</v>
       </c>
       <c r="V21" t="n">
         <v>1118.662488620264</v>
       </c>
       <c r="W21" t="n">
-        <v>746.9453169030926</v>
+        <v>784.9578301928352</v>
       </c>
       <c r="X21" t="n">
-        <v>727.8920447360344</v>
+        <v>765.9045580257771</v>
       </c>
       <c r="Y21" t="n">
-        <v>727.8920447360344</v>
+        <v>765.9045580257771</v>
       </c>
     </row>
     <row r="22">
@@ -5877,31 +5877,31 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>373.6390559156168</v>
+        <v>541.4438642070763</v>
       </c>
       <c r="C22" t="n">
-        <v>373.6390559156168</v>
+        <v>668.4358700255121</v>
       </c>
       <c r="D22" t="n">
-        <v>373.6390559156168</v>
+        <v>782.7450141505122</v>
       </c>
       <c r="E22" t="n">
-        <v>373.6390559156168</v>
+        <v>901.5639183619253</v>
       </c>
       <c r="F22" t="n">
-        <v>373.6390559156168</v>
+        <v>1026.914890953861</v>
       </c>
       <c r="G22" t="n">
-        <v>528.2427103270923</v>
+        <v>1181.518545365336</v>
       </c>
       <c r="H22" t="n">
-        <v>700.5905007323914</v>
+        <v>1353.866335770635</v>
       </c>
       <c r="I22" t="n">
-        <v>928.9410963897858</v>
+        <v>1353.866335770635</v>
       </c>
       <c r="J22" t="n">
-        <v>1218.451980522291</v>
+        <v>1353.866335770635</v>
       </c>
       <c r="K22" t="n">
         <v>1353.866335770635</v>
@@ -5916,37 +5916,37 @@
         <v>1135.043282077439</v>
       </c>
       <c r="O22" t="n">
-        <v>923.0444178810503</v>
+        <v>923.0444178810502</v>
       </c>
       <c r="P22" t="n">
         <v>659.258066878816</v>
       </c>
       <c r="Q22" t="n">
-        <v>348.8305250347775</v>
+        <v>348.8305250347776</v>
       </c>
       <c r="R22" t="n">
         <v>29.44</v>
       </c>
       <c r="S22" t="n">
-        <v>71.28924329089443</v>
+        <v>29.44</v>
       </c>
       <c r="T22" t="n">
-        <v>261.2397552365845</v>
+        <v>164.2764348375584</v>
       </c>
       <c r="U22" t="n">
-        <v>261.2397552365845</v>
+        <v>164.2764348375584</v>
       </c>
       <c r="V22" t="n">
-        <v>261.2397552365845</v>
+        <v>164.2764348375584</v>
       </c>
       <c r="W22" t="n">
-        <v>261.2397552365845</v>
+        <v>164.2764348375584</v>
       </c>
       <c r="X22" t="n">
-        <v>261.2397552365845</v>
+        <v>316.2972258617519</v>
       </c>
       <c r="Y22" t="n">
-        <v>373.6390559156168</v>
+        <v>428.6965265407842</v>
       </c>
     </row>
     <row r="23">
@@ -5971,7 +5971,7 @@
         <v>34.0105860977523</v>
       </c>
       <c r="G23" t="n">
-        <v>31.69640364449496</v>
+        <v>31.69640364449497</v>
       </c>
       <c r="H23" t="n">
         <v>29.44</v>
@@ -5983,19 +5983,19 @@
         <v>33.93094723444601</v>
       </c>
       <c r="K23" t="n">
-        <v>92.65689155605405</v>
+        <v>231.8404470522923</v>
       </c>
       <c r="L23" t="n">
-        <v>165.5116183902249</v>
+        <v>304.6951738864632</v>
       </c>
       <c r="M23" t="n">
-        <v>165.5116183902249</v>
+        <v>669.0151738864639</v>
       </c>
       <c r="N23" t="n">
-        <v>379.0399999999979</v>
+        <v>1033.335173886465</v>
       </c>
       <c r="O23" t="n">
-        <v>743.3599999999986</v>
+        <v>1041.575704817158</v>
       </c>
       <c r="P23" t="n">
         <v>1107.679999999999</v>
@@ -6035,7 +6035,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>357.1852404199512</v>
+        <v>29.44</v>
       </c>
       <c r="C24" t="n">
         <v>29.44</v>
@@ -6074,37 +6074,37 @@
         <v>1076.99110421531</v>
       </c>
       <c r="O24" t="n">
-        <v>1312.301750624833</v>
+        <v>1374.804550993368</v>
       </c>
       <c r="P24" t="n">
         <v>1472</v>
       </c>
       <c r="Q24" t="n">
-        <v>1329.34383362311</v>
+        <v>1341.62572157707</v>
       </c>
       <c r="R24" t="n">
-        <v>1197.240474436983</v>
+        <v>1209.522362390943</v>
       </c>
       <c r="S24" t="n">
-        <v>1135.695553565544</v>
+        <v>1147.977441519504</v>
       </c>
       <c r="T24" t="n">
-        <v>1132.309627197557</v>
+        <v>1144.591515151518</v>
       </c>
       <c r="U24" t="n">
-        <v>1132.309627197557</v>
+        <v>1144.591515151518</v>
       </c>
       <c r="V24" t="n">
-        <v>760.5924554803848</v>
+        <v>772.8743434343451</v>
       </c>
       <c r="W24" t="n">
-        <v>728.9024121371237</v>
+        <v>401.1571717171725</v>
       </c>
       <c r="X24" t="n">
-        <v>357.1852404199512</v>
+        <v>29.44</v>
       </c>
       <c r="Y24" t="n">
-        <v>357.1852404199512</v>
+        <v>29.44</v>
       </c>
     </row>
     <row r="25">
@@ -6114,34 +6114,34 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>779.2997405151413</v>
+        <v>732.980953775507</v>
       </c>
       <c r="C25" t="n">
-        <v>906.2917463335771</v>
+        <v>859.9729595939428</v>
       </c>
       <c r="D25" t="n">
-        <v>1020.600890458577</v>
+        <v>974.2821037189429</v>
       </c>
       <c r="E25" t="n">
-        <v>1020.600890458577</v>
+        <v>1093.101007930356</v>
       </c>
       <c r="F25" t="n">
-        <v>1020.600890458577</v>
+        <v>1218.451980522291</v>
       </c>
       <c r="G25" t="n">
-        <v>1175.204544870053</v>
+        <v>1218.451980522291</v>
       </c>
       <c r="H25" t="n">
-        <v>1347.552335275352</v>
+        <v>1218.451980522291</v>
       </c>
       <c r="I25" t="n">
-        <v>1362.332599632139</v>
+        <v>1218.451980522291</v>
       </c>
       <c r="J25" t="n">
-        <v>1362.332599632139</v>
+        <v>1218.451980522291</v>
       </c>
       <c r="K25" t="n">
-        <v>1362.332599632139</v>
+        <v>1353.866335770635</v>
       </c>
       <c r="L25" t="n">
         <v>1362.332599632139</v>
@@ -6153,13 +6153,13 @@
         <v>1135.043282077439</v>
       </c>
       <c r="O25" t="n">
-        <v>923.0444178810502</v>
+        <v>923.0444178810503</v>
       </c>
       <c r="P25" t="n">
         <v>659.258066878816</v>
       </c>
       <c r="Q25" t="n">
-        <v>348.8305250347776</v>
+        <v>348.8305250347775</v>
       </c>
       <c r="R25" t="n">
         <v>29.44</v>
@@ -6168,22 +6168,22 @@
         <v>29.44</v>
       </c>
       <c r="T25" t="n">
-        <v>29.44</v>
+        <v>219.3905119456901</v>
       </c>
       <c r="U25" t="n">
-        <v>29.44</v>
+        <v>466.9430003216817</v>
       </c>
       <c r="V25" t="n">
-        <v>229.251392885946</v>
+        <v>466.9430003216817</v>
       </c>
       <c r="W25" t="n">
-        <v>402.1323111456234</v>
+        <v>466.9430003216817</v>
       </c>
       <c r="X25" t="n">
-        <v>554.1531021698169</v>
+        <v>507.8343154301827</v>
       </c>
       <c r="Y25" t="n">
-        <v>666.5524028488492</v>
+        <v>620.2336161092149</v>
       </c>
     </row>
     <row r="26">
@@ -6193,22 +6193,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>26.08</v>
+        <v>360.017420766723</v>
       </c>
       <c r="C26" t="n">
-        <v>26.08</v>
+        <v>218.1239073899615</v>
       </c>
       <c r="D26" t="n">
-        <v>26.08</v>
+        <v>218.1239073899615</v>
       </c>
       <c r="E26" t="n">
-        <v>26.08</v>
+        <v>218.1239073899615</v>
       </c>
       <c r="F26" t="n">
-        <v>26.08</v>
+        <v>121.2656965737879</v>
       </c>
       <c r="G26" t="n">
-        <v>26.08</v>
+        <v>121.2656965737879</v>
       </c>
       <c r="H26" t="n">
         <v>26.08</v>
@@ -6217,25 +6217,25 @@
         <v>26.08</v>
       </c>
       <c r="J26" t="n">
-        <v>348.82</v>
+        <v>30.57094723444601</v>
       </c>
       <c r="K26" t="n">
-        <v>407.545944321608</v>
+        <v>89.29689155605405</v>
       </c>
       <c r="L26" t="n">
-        <v>480.4006711557789</v>
+        <v>261.4351738864652</v>
       </c>
       <c r="M26" t="n">
-        <v>803.1406711557789</v>
+        <v>584.1751738864652</v>
       </c>
       <c r="N26" t="n">
-        <v>1125.880671155779</v>
+        <v>906.9151738864653</v>
       </c>
       <c r="O26" t="n">
-        <v>1134.121202086473</v>
+        <v>915.1557048171589</v>
       </c>
       <c r="P26" t="n">
-        <v>1200.225497269314</v>
+        <v>981.26</v>
       </c>
       <c r="Q26" t="n">
         <v>1304</v>
@@ -6250,19 +6250,19 @@
         <v>1304</v>
       </c>
       <c r="U26" t="n">
-        <v>974.7070707070707</v>
+        <v>1150.200396944763</v>
       </c>
       <c r="V26" t="n">
-        <v>845.8772385287618</v>
+        <v>1150.200396944763</v>
       </c>
       <c r="W26" t="n">
-        <v>516.5843092358325</v>
+        <v>820.9074676518162</v>
       </c>
       <c r="X26" t="n">
-        <v>230.4410431139459</v>
+        <v>534.7642015299296</v>
       </c>
       <c r="Y26" t="n">
-        <v>26.08</v>
+        <v>534.7642015299296</v>
       </c>
     </row>
     <row r="27">
@@ -6296,10 +6296,10 @@
         <v>26.08</v>
       </c>
       <c r="J27" t="n">
-        <v>173.3739582885065</v>
+        <v>26.08</v>
       </c>
       <c r="K27" t="n">
-        <v>177.5553646661583</v>
+        <v>255.1602149623079</v>
       </c>
       <c r="L27" t="n">
         <v>500.2953646661583</v>
@@ -6354,25 +6354,25 @@
         <v>575.882740836823</v>
       </c>
       <c r="C28" t="n">
-        <v>606.7296840081626</v>
+        <v>611.7947466552588</v>
       </c>
       <c r="D28" t="n">
-        <v>629.9588281331627</v>
+        <v>635.0238907802589</v>
       </c>
       <c r="E28" t="n">
-        <v>657.6977323445757</v>
+        <v>662.7627949916719</v>
       </c>
       <c r="F28" t="n">
-        <v>691.9687049365111</v>
+        <v>697.0337675836073</v>
       </c>
       <c r="G28" t="n">
-        <v>755.4923593479865</v>
+        <v>760.5574219950827</v>
       </c>
       <c r="H28" t="n">
-        <v>836.7601497532858</v>
+        <v>841.8252124003819</v>
       </c>
       <c r="I28" t="n">
-        <v>974.0307454106802</v>
+        <v>979.0958080577764</v>
       </c>
       <c r="J28" t="n">
         <v>1259.665644751656</v>
@@ -6381,25 +6381,25 @@
         <v>1304</v>
       </c>
       <c r="L28" t="n">
-        <v>1219.708870382108</v>
+        <v>1304</v>
       </c>
       <c r="M28" t="n">
-        <v>1219.708870382108</v>
+        <v>1304</v>
       </c>
       <c r="N28" t="n">
-        <v>987.2090924126957</v>
+        <v>1071.500222030588</v>
       </c>
       <c r="O28" t="n">
-        <v>987.2090924126957</v>
+        <v>1064.189128363638</v>
       </c>
       <c r="P28" t="n">
-        <v>657.9161631197663</v>
+        <v>734.896199070674</v>
       </c>
       <c r="Q28" t="n">
-        <v>355.3729292929293</v>
+        <v>405.6032697777134</v>
       </c>
       <c r="R28" t="n">
-        <v>26.08</v>
+        <v>76.31034048475215</v>
       </c>
       <c r="S28" t="n">
         <v>26.08</v>
@@ -6430,22 +6430,22 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>372.1967282209929</v>
+        <v>314.508241357177</v>
       </c>
       <c r="C29" t="n">
-        <v>372.1967282209929</v>
+        <v>314.508241357177</v>
       </c>
       <c r="D29" t="n">
-        <v>372.1967282209929</v>
+        <v>314.508241357177</v>
       </c>
       <c r="E29" t="n">
-        <v>313.3673827725117</v>
+        <v>218.1816861987239</v>
       </c>
       <c r="F29" t="n">
-        <v>216.5091719563382</v>
+        <v>121.3234753825503</v>
       </c>
       <c r="G29" t="n">
-        <v>121.2656965737879</v>
+        <v>26.08</v>
       </c>
       <c r="H29" t="n">
         <v>26.08</v>
@@ -6484,22 +6484,22 @@
         <v>1304</v>
       </c>
       <c r="T29" t="n">
-        <v>1025.581601116775</v>
+        <v>1304</v>
       </c>
       <c r="U29" t="n">
-        <v>696.2886718238453</v>
+        <v>974.7070707070707</v>
       </c>
       <c r="V29" t="n">
-        <v>372.1967282209929</v>
+        <v>650.6151271042182</v>
       </c>
       <c r="W29" t="n">
-        <v>372.1967282209929</v>
+        <v>321.3221978112889</v>
       </c>
       <c r="X29" t="n">
-        <v>372.1967282209929</v>
+        <v>314.508241357177</v>
       </c>
       <c r="Y29" t="n">
-        <v>372.1967282209929</v>
+        <v>314.508241357177</v>
       </c>
     </row>
     <row r="30">
@@ -6509,25 +6509,25 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>220.6197138196374</v>
+        <v>225.2602949632918</v>
       </c>
       <c r="C30" t="n">
-        <v>167.9935396322442</v>
+        <v>172.6341207758985</v>
       </c>
       <c r="D30" t="n">
-        <v>128.6625427658779</v>
+        <v>133.3031239095322</v>
       </c>
       <c r="E30" t="n">
-        <v>94.65032334980452</v>
+        <v>99.29090449345887</v>
       </c>
       <c r="F30" t="n">
-        <v>63.70462401861577</v>
+        <v>68.3452051622701</v>
       </c>
       <c r="G30" t="n">
-        <v>47.04803165390356</v>
+        <v>51.6886127975579</v>
       </c>
       <c r="H30" t="n">
-        <v>26.08</v>
+        <v>30.72058114365434</v>
       </c>
       <c r="I30" t="n">
         <v>26.08</v>
@@ -6554,31 +6554,31 @@
         <v>1304</v>
       </c>
       <c r="Q30" t="n">
-        <v>1299.359418856346</v>
+        <v>1304</v>
       </c>
       <c r="R30" t="n">
-        <v>1074.326766740925</v>
+        <v>1078.96734788458</v>
       </c>
       <c r="S30" t="n">
-        <v>919.8525529401936</v>
+        <v>924.493134083848</v>
       </c>
       <c r="T30" t="n">
-        <v>823.5373336429145</v>
+        <v>828.1779147865689</v>
       </c>
       <c r="U30" t="n">
-        <v>731.4222380208467</v>
+        <v>736.0628191645011</v>
       </c>
       <c r="V30" t="n">
-        <v>624.8458065142607</v>
+        <v>629.4863876579151</v>
       </c>
       <c r="W30" t="n">
-        <v>500.2264702417067</v>
+        <v>504.867051385361</v>
       </c>
       <c r="X30" t="n">
-        <v>388.2439051453556</v>
+        <v>392.8844862890099</v>
       </c>
       <c r="Y30" t="n">
-        <v>296.9394680078461</v>
+        <v>301.5800491515005</v>
       </c>
     </row>
     <row r="31">
@@ -6594,22 +6594,22 @@
         <v>611.7947466552588</v>
       </c>
       <c r="D31" t="n">
-        <v>635.0238907802589</v>
+        <v>629.9588281331627</v>
       </c>
       <c r="E31" t="n">
-        <v>662.7627949916719</v>
+        <v>657.6977323445757</v>
       </c>
       <c r="F31" t="n">
-        <v>697.0337675836073</v>
+        <v>691.9687049365111</v>
       </c>
       <c r="G31" t="n">
-        <v>760.5574219950827</v>
+        <v>755.4923593479865</v>
       </c>
       <c r="H31" t="n">
-        <v>841.8252124003819</v>
+        <v>836.7601497532858</v>
       </c>
       <c r="I31" t="n">
-        <v>979.0958080577764</v>
+        <v>974.0307454106802</v>
       </c>
       <c r="J31" t="n">
         <v>1259.665644751656</v>
@@ -6627,16 +6627,16 @@
         <v>1304</v>
       </c>
       <c r="O31" t="n">
-        <v>999.0718428743185</v>
+        <v>1064.18912836354</v>
       </c>
       <c r="P31" t="n">
-        <v>669.7789135813891</v>
+        <v>734.8961990706108</v>
       </c>
       <c r="Q31" t="n">
-        <v>355.3729292929293</v>
+        <v>405.6032697776815</v>
       </c>
       <c r="R31" t="n">
-        <v>26.08</v>
+        <v>76.31034048475215</v>
       </c>
       <c r="S31" t="n">
         <v>26.08</v>
@@ -6691,16 +6691,16 @@
         <v>24.32</v>
       </c>
       <c r="J32" t="n">
-        <v>28.810947234446</v>
+        <v>325.2800000000018</v>
       </c>
       <c r="K32" t="n">
-        <v>87.53689155605404</v>
+        <v>384.0059443216099</v>
       </c>
       <c r="L32" t="n">
-        <v>388.496891556054</v>
+        <v>456.8606711557807</v>
       </c>
       <c r="M32" t="n">
-        <v>539.7351738864616</v>
+        <v>757.8206711557826</v>
       </c>
       <c r="N32" t="n">
         <v>840.6951738864634</v>
@@ -6715,7 +6715,7 @@
         <v>1216</v>
       </c>
       <c r="R32" t="n">
-        <v>1214.559896504203</v>
+        <v>1216</v>
       </c>
       <c r="S32" t="n">
         <v>1156.760265050661</v>
@@ -6746,25 +6746,25 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>460.7355583262683</v>
+        <v>24.32</v>
       </c>
       <c r="C33" t="n">
-        <v>234.9622422763765</v>
+        <v>24.32</v>
       </c>
       <c r="D33" t="n">
-        <v>234.9622422763765</v>
+        <v>24.32</v>
       </c>
       <c r="E33" t="n">
-        <v>234.9622422763765</v>
+        <v>24.32</v>
       </c>
       <c r="F33" t="n">
-        <v>234.9622422763765</v>
+        <v>24.32</v>
       </c>
       <c r="G33" t="n">
-        <v>234.9622422763765</v>
+        <v>24.32</v>
       </c>
       <c r="H33" t="n">
-        <v>234.9622422763765</v>
+        <v>24.32</v>
       </c>
       <c r="I33" t="n">
         <v>24.32</v>
@@ -6773,49 +6773,49 @@
         <v>24.32</v>
       </c>
       <c r="K33" t="n">
-        <v>111.3353646661565</v>
+        <v>253.4002149623079</v>
       </c>
       <c r="L33" t="n">
-        <v>412.2953646661583</v>
+        <v>554.3602149623098</v>
       </c>
       <c r="M33" t="n">
-        <v>560.9637064090175</v>
+        <v>703.028556705169</v>
       </c>
       <c r="N33" t="n">
-        <v>758.4883038467744</v>
+        <v>900.5531541429259</v>
       </c>
       <c r="O33" t="n">
-        <v>1056.301750624833</v>
+        <v>1198.366600920984</v>
       </c>
       <c r="P33" t="n">
         <v>1216</v>
       </c>
       <c r="Q33" t="n">
-        <v>1216</v>
+        <v>1073.34383362311</v>
       </c>
       <c r="R33" t="n">
-        <v>1110.159267076499</v>
+        <v>766.273126552401</v>
       </c>
       <c r="S33" t="n">
-        <v>1074.876972467686</v>
+        <v>459.202419481692</v>
       </c>
       <c r="T33" t="n">
-        <v>767.8062653969773</v>
+        <v>152.131712410983</v>
       </c>
       <c r="U33" t="n">
-        <v>767.8062653969773</v>
+        <v>152.131712410983</v>
       </c>
       <c r="V33" t="n">
-        <v>767.8062653969773</v>
+        <v>152.131712410983</v>
       </c>
       <c r="W33" t="n">
-        <v>460.7355583262683</v>
+        <v>146.7042953303482</v>
       </c>
       <c r="X33" t="n">
-        <v>460.7355583262683</v>
+        <v>24.32</v>
       </c>
       <c r="Y33" t="n">
-        <v>460.7355583262683</v>
+        <v>24.32</v>
       </c>
     </row>
     <row r="34">
@@ -6825,25 +6825,25 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>538.8410099629032</v>
+        <v>857.5188819579004</v>
       </c>
       <c r="C34" t="n">
-        <v>538.8410099629032</v>
+        <v>874.7342834334926</v>
       </c>
       <c r="D34" t="n">
-        <v>678.8901540879033</v>
+        <v>874.7342834334926</v>
       </c>
       <c r="E34" t="n">
-        <v>678.8901540879033</v>
+        <v>1019.293187644906</v>
       </c>
       <c r="F34" t="n">
-        <v>747.4584559936875</v>
+        <v>1019.293187644906</v>
       </c>
       <c r="G34" t="n">
-        <v>747.4584559936875</v>
+        <v>1199.636842056381</v>
       </c>
       <c r="H34" t="n">
-        <v>945.5462463989867</v>
+        <v>1199.636842056381</v>
       </c>
       <c r="I34" t="n">
         <v>1199.636842056381</v>
@@ -6876,25 +6876,25 @@
         <v>24.32</v>
       </c>
       <c r="S34" t="n">
-        <v>24.32</v>
+        <v>91.90924329089444</v>
       </c>
       <c r="T34" t="n">
-        <v>24.32</v>
+        <v>307.5997552365845</v>
       </c>
       <c r="U34" t="n">
-        <v>24.32</v>
+        <v>580.8922436125761</v>
       </c>
       <c r="V34" t="n">
-        <v>24.32</v>
+        <v>580.8922436125761</v>
       </c>
       <c r="W34" t="n">
-        <v>222.9409182596774</v>
+        <v>580.8922436125761</v>
       </c>
       <c r="X34" t="n">
-        <v>400.7017092838709</v>
+        <v>580.8922436125761</v>
       </c>
       <c r="Y34" t="n">
-        <v>538.8410099629032</v>
+        <v>719.0315442916083</v>
       </c>
     </row>
     <row r="35">
@@ -6934,19 +6934,19 @@
         <v>86.57689155605404</v>
       </c>
       <c r="L35" t="n">
-        <v>226.4151738864654</v>
+        <v>159.4316183902249</v>
       </c>
       <c r="M35" t="n">
-        <v>515.4951738864654</v>
+        <v>448.5116183902323</v>
       </c>
       <c r="N35" t="n">
-        <v>804.5751738864653</v>
+        <v>737.5916183902397</v>
       </c>
       <c r="O35" t="n">
-        <v>812.815704817159</v>
+        <v>1026.671618390247</v>
       </c>
       <c r="P35" t="n">
-        <v>878.9200000000001</v>
+        <v>1092.775913573088</v>
       </c>
       <c r="Q35" t="n">
         <v>1168</v>
@@ -6961,16 +6961,16 @@
         <v>961.0748989561623</v>
       </c>
       <c r="U35" t="n">
-        <v>741.6971312632862</v>
+        <v>741.6971312632861</v>
       </c>
       <c r="V35" t="n">
-        <v>541.847611902858</v>
+        <v>541.8476119028579</v>
       </c>
       <c r="W35" t="n">
-        <v>333.5349064061036</v>
+        <v>333.3895553564462</v>
       </c>
       <c r="X35" t="n">
-        <v>171.6340645266412</v>
+        <v>171.4887134769839</v>
       </c>
       <c r="Y35" t="n">
         <v>91.51544565511962</v>
@@ -6983,16 +6983,16 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>613.25898989899</v>
+        <v>893.9449041616765</v>
       </c>
       <c r="C36" t="n">
-        <v>613.25898989899</v>
+        <v>613.258989899005</v>
       </c>
       <c r="D36" t="n">
-        <v>613.25898989899</v>
+        <v>318.3094949495025</v>
       </c>
       <c r="E36" t="n">
-        <v>318.309494949495</v>
+        <v>318.3094949495025</v>
       </c>
       <c r="F36" t="n">
         <v>23.36</v>
@@ -7013,16 +7013,16 @@
         <v>399.7341732508144</v>
       </c>
       <c r="L36" t="n">
-        <v>532.727060819384</v>
+        <v>688.8141732508218</v>
       </c>
       <c r="M36" t="n">
-        <v>681.3954025622431</v>
+        <v>688.8141732508218</v>
       </c>
       <c r="N36" t="n">
-        <v>878.9200000000001</v>
+        <v>886.3387706885787</v>
       </c>
       <c r="O36" t="n">
-        <v>1168</v>
+        <v>1008.301750624833</v>
       </c>
       <c r="P36" t="n">
         <v>1168</v>
@@ -7049,10 +7049,10 @@
         <v>893.9449041616765</v>
       </c>
       <c r="X36" t="n">
-        <v>613.25898989899</v>
+        <v>893.9449041616765</v>
       </c>
       <c r="Y36" t="n">
-        <v>613.25898989899</v>
+        <v>893.9449041616765</v>
       </c>
     </row>
     <row r="37">
@@ -7062,31 +7062,31 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>513.4575566050019</v>
+        <v>625.2702532537976</v>
       </c>
       <c r="C37" t="n">
-        <v>671.1395624234376</v>
+        <v>782.9522590722333</v>
       </c>
       <c r="D37" t="n">
-        <v>671.1395624234376</v>
+        <v>927.9514031972334</v>
       </c>
       <c r="E37" t="n">
-        <v>671.1395624234376</v>
+        <v>1077.460307408646</v>
       </c>
       <c r="F37" t="n">
-        <v>827.1805350153732</v>
+        <v>1077.460307408646</v>
       </c>
       <c r="G37" t="n">
-        <v>1012.474189426849</v>
+        <v>1077.460307408646</v>
       </c>
       <c r="H37" t="n">
-        <v>1168</v>
+        <v>1077.460307408646</v>
       </c>
       <c r="I37" t="n">
-        <v>1168</v>
+        <v>1077.460307408646</v>
       </c>
       <c r="J37" t="n">
-        <v>1168</v>
+        <v>1077.460307408646</v>
       </c>
       <c r="K37" t="n">
         <v>1168</v>
@@ -7095,43 +7095,43 @@
         <v>1168</v>
       </c>
       <c r="M37" t="n">
-        <v>1111.59429879855</v>
+        <v>1111.968110551901</v>
       </c>
       <c r="N37" t="n">
-        <v>1003.336945071563</v>
+        <v>1003.710756824914</v>
       </c>
       <c r="O37" t="n">
-        <v>823.0250239416564</v>
+        <v>823.0250239416563</v>
       </c>
       <c r="P37" t="n">
-        <v>590.5518042525534</v>
+        <v>590.5518042525533</v>
       </c>
       <c r="Q37" t="n">
-        <v>311.4373937216463</v>
+        <v>311.4373937216462</v>
       </c>
       <c r="R37" t="n">
         <v>23.36</v>
       </c>
       <c r="S37" t="n">
-        <v>23.36</v>
+        <v>95.89924329089443</v>
       </c>
       <c r="T37" t="n">
-        <v>23.36</v>
+        <v>95.89924329089443</v>
       </c>
       <c r="U37" t="n">
-        <v>23.36</v>
+        <v>95.89924329089443</v>
       </c>
       <c r="V37" t="n">
-        <v>23.36</v>
+        <v>95.89924329089443</v>
       </c>
       <c r="W37" t="n">
-        <v>226.9309182596774</v>
+        <v>299.4701615505718</v>
       </c>
       <c r="X37" t="n">
-        <v>226.9309182596774</v>
+        <v>482.1809525747653</v>
       </c>
       <c r="Y37" t="n">
-        <v>370.0202189387097</v>
+        <v>625.2702532537976</v>
       </c>
     </row>
     <row r="38">
@@ -7168,22 +7168,22 @@
         <v>27.850947234446</v>
       </c>
       <c r="K38" t="n">
-        <v>316.930947234446</v>
+        <v>86.57689155605404</v>
       </c>
       <c r="L38" t="n">
-        <v>389.7856740686169</v>
+        <v>226.4151738864218</v>
       </c>
       <c r="M38" t="n">
-        <v>678.8656740686168</v>
+        <v>515.4951738864363</v>
       </c>
       <c r="N38" t="n">
-        <v>967.9456740686169</v>
+        <v>804.5751738864508</v>
       </c>
       <c r="O38" t="n">
-        <v>976.1862049993106</v>
+        <v>812.8157048171445</v>
       </c>
       <c r="P38" t="n">
-        <v>1042.290500182152</v>
+        <v>878.9199999999855</v>
       </c>
       <c r="Q38" t="n">
         <v>1168</v>
@@ -7192,16 +7192,16 @@
         <v>1168</v>
       </c>
       <c r="S38" t="n">
-        <v>1115.250873596963</v>
+        <v>1115.396224646621</v>
       </c>
       <c r="T38" t="n">
-        <v>961.0748989561623</v>
+        <v>961.2202500058195</v>
       </c>
       <c r="U38" t="n">
-        <v>741.6971312632862</v>
+        <v>741.8424823129434</v>
       </c>
       <c r="V38" t="n">
-        <v>541.847611902858</v>
+        <v>541.9929629525152</v>
       </c>
       <c r="W38" t="n">
         <v>333.5349064061036</v>
@@ -7220,16 +7220,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>23.36</v>
+        <v>893.9449041616765</v>
       </c>
       <c r="C39" t="n">
-        <v>23.36</v>
+        <v>613.2589898990194</v>
       </c>
       <c r="D39" t="n">
-        <v>23.36</v>
+        <v>613.2589898990194</v>
       </c>
       <c r="E39" t="n">
-        <v>23.36</v>
+        <v>318.3094949495097</v>
       </c>
       <c r="F39" t="n">
         <v>23.36</v>
@@ -7250,46 +7250,46 @@
         <v>399.7341732508144</v>
       </c>
       <c r="L39" t="n">
-        <v>662.1088114442168</v>
+        <v>688.8141732508288</v>
       </c>
       <c r="M39" t="n">
-        <v>810.777153187076</v>
+        <v>837.482514993688</v>
       </c>
       <c r="N39" t="n">
-        <v>1008.301750624833</v>
+        <v>1035.007112431445</v>
       </c>
       <c r="O39" t="n">
-        <v>1008.301750624833</v>
+        <v>1168</v>
       </c>
       <c r="P39" t="n">
         <v>1168</v>
       </c>
       <c r="Q39" t="n">
-        <v>1168</v>
+        <v>1025.34383362311</v>
       </c>
       <c r="R39" t="n">
-        <v>1067.209772127004</v>
+        <v>924.5536057501139</v>
       </c>
       <c r="S39" t="n">
-        <v>1036.977982568696</v>
+        <v>894.3218161918063</v>
       </c>
       <c r="T39" t="n">
-        <v>1036.977982568696</v>
+        <v>894.3218161918063</v>
       </c>
       <c r="U39" t="n">
-        <v>742.0284876192013</v>
+        <v>894.3218161918063</v>
       </c>
       <c r="V39" t="n">
-        <v>447.0789926697063</v>
+        <v>894.3218161918063</v>
       </c>
       <c r="W39" t="n">
-        <v>152.1294977202114</v>
+        <v>893.9449041616765</v>
       </c>
       <c r="X39" t="n">
-        <v>23.36</v>
+        <v>893.9449041616765</v>
       </c>
       <c r="Y39" t="n">
-        <v>23.36</v>
+        <v>893.9449041616765</v>
       </c>
     </row>
     <row r="40">
@@ -7299,76 +7299,76 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1168</v>
+        <v>806.6984082982171</v>
       </c>
       <c r="C40" t="n">
-        <v>1168</v>
+        <v>806.6984082982171</v>
       </c>
       <c r="D40" t="n">
-        <v>1168</v>
+        <v>806.6984082982171</v>
       </c>
       <c r="E40" t="n">
-        <v>1168</v>
+        <v>806.6984082982171</v>
       </c>
       <c r="F40" t="n">
-        <v>1168</v>
+        <v>962.7393808901527</v>
       </c>
       <c r="G40" t="n">
-        <v>1168</v>
+        <v>962.7393808901527</v>
       </c>
       <c r="H40" t="n">
-        <v>1168</v>
+        <v>962.7393808901527</v>
       </c>
       <c r="I40" t="n">
-        <v>1168</v>
+        <v>962.7393808901527</v>
       </c>
       <c r="J40" t="n">
-        <v>1168</v>
+        <v>962.7393808901527</v>
       </c>
       <c r="K40" t="n">
-        <v>1168</v>
+        <v>1128.843736138497</v>
       </c>
       <c r="L40" t="n">
         <v>1168</v>
       </c>
       <c r="M40" t="n">
-        <v>1111.59429879855</v>
+        <v>1111.968110551901</v>
       </c>
       <c r="N40" t="n">
-        <v>1003.336945071563</v>
+        <v>1003.710756824914</v>
       </c>
       <c r="O40" t="n">
-        <v>823.0250239416564</v>
+        <v>823.0250239416563</v>
       </c>
       <c r="P40" t="n">
-        <v>590.5518042525534</v>
+        <v>590.5518042525533</v>
       </c>
       <c r="Q40" t="n">
-        <v>311.4373937216463</v>
+        <v>311.4373937216462</v>
       </c>
       <c r="R40" t="n">
         <v>23.36</v>
       </c>
       <c r="S40" t="n">
-        <v>95.89924329089445</v>
+        <v>95.89924329089443</v>
       </c>
       <c r="T40" t="n">
-        <v>316.5397552365846</v>
+        <v>316.5397552365845</v>
       </c>
       <c r="U40" t="n">
-        <v>551.2168978301831</v>
+        <v>594.7822436125762</v>
       </c>
       <c r="V40" t="n">
-        <v>781.7182907161291</v>
+        <v>663.6091076191849</v>
       </c>
       <c r="W40" t="n">
-        <v>985.2892089758064</v>
+        <v>663.6091076191849</v>
       </c>
       <c r="X40" t="n">
-        <v>1168</v>
+        <v>663.6091076191849</v>
       </c>
       <c r="Y40" t="n">
-        <v>1168</v>
+        <v>806.6984082982171</v>
       </c>
     </row>
     <row r="41">
@@ -7378,19 +7378,19 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>23.36</v>
+        <v>515.640497905504</v>
       </c>
       <c r="C41" t="n">
-        <v>23.36</v>
+        <v>381.8277926095506</v>
       </c>
       <c r="D41" t="n">
-        <v>23.36</v>
+        <v>287.5458171147528</v>
       </c>
       <c r="E41" t="n">
-        <v>23.36</v>
+        <v>199.3000700371077</v>
       </c>
       <c r="F41" t="n">
-        <v>23.36</v>
+        <v>110.5226673017422</v>
       </c>
       <c r="G41" t="n">
         <v>23.36</v>
@@ -7402,25 +7402,25 @@
         <v>23.36</v>
       </c>
       <c r="J41" t="n">
-        <v>27.850947234446</v>
+        <v>175.9297604955036</v>
       </c>
       <c r="K41" t="n">
-        <v>86.57689155605404</v>
+        <v>234.6557048171116</v>
       </c>
       <c r="L41" t="n">
-        <v>226.4151738864654</v>
+        <v>523.7357048171116</v>
       </c>
       <c r="M41" t="n">
-        <v>515.4951738864654</v>
+        <v>523.7357048171116</v>
       </c>
       <c r="N41" t="n">
-        <v>804.5751738864653</v>
+        <v>812.8157048171353</v>
       </c>
       <c r="O41" t="n">
-        <v>812.815704817159</v>
+        <v>1101.895704817159</v>
       </c>
       <c r="P41" t="n">
-        <v>878.9200000000001</v>
+        <v>1168</v>
       </c>
       <c r="Q41" t="n">
         <v>1168</v>
@@ -7432,22 +7432,22 @@
         <v>1168</v>
       </c>
       <c r="T41" t="n">
-        <v>897.6624091975827</v>
+        <v>1168</v>
       </c>
       <c r="U41" t="n">
-        <v>613.25898989899</v>
+        <v>1168</v>
       </c>
       <c r="V41" t="n">
-        <v>318.309494949495</v>
+        <v>1168</v>
       </c>
       <c r="W41" t="n">
-        <v>23.36</v>
+        <v>1156.649163662119</v>
       </c>
       <c r="X41" t="n">
-        <v>23.36</v>
+        <v>878.5867056210404</v>
       </c>
       <c r="Y41" t="n">
-        <v>23.36</v>
+        <v>682.3064705879026</v>
       </c>
     </row>
     <row r="42">
@@ -7484,19 +7484,19 @@
         <v>170.6539582885065</v>
       </c>
       <c r="K42" t="n">
-        <v>243.647060819384</v>
+        <v>170.6539582885065</v>
       </c>
       <c r="L42" t="n">
-        <v>532.727060819384</v>
+        <v>373.0288114441931</v>
       </c>
       <c r="M42" t="n">
-        <v>681.3954025622431</v>
+        <v>521.6971531870523</v>
       </c>
       <c r="N42" t="n">
-        <v>878.9200000000001</v>
+        <v>719.2217506248093</v>
       </c>
       <c r="O42" t="n">
-        <v>1168</v>
+        <v>1008.301750624833</v>
       </c>
       <c r="P42" t="n">
         <v>1168</v>
@@ -7536,28 +7536,28 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>599.0154031705308</v>
+        <v>628.6027408368229</v>
       </c>
       <c r="C43" t="n">
-        <v>642.8474089889665</v>
+        <v>672.4347466552587</v>
       </c>
       <c r="D43" t="n">
-        <v>642.8474089889665</v>
+        <v>703.5838907802587</v>
       </c>
       <c r="E43" t="n">
-        <v>678.5063132003796</v>
+        <v>739.2427949916718</v>
       </c>
       <c r="F43" t="n">
-        <v>720.6972857923151</v>
+        <v>781.4337675836073</v>
       </c>
       <c r="G43" t="n">
-        <v>792.1409402037906</v>
+        <v>852.8774219950827</v>
       </c>
       <c r="H43" t="n">
-        <v>881.3287306090898</v>
+        <v>942.0652124003819</v>
       </c>
       <c r="I43" t="n">
-        <v>1026.519326266484</v>
+        <v>1087.255808057776</v>
       </c>
       <c r="J43" t="n">
         <v>1115.745644751656</v>
@@ -7566,25 +7566,25 @@
         <v>1168</v>
       </c>
       <c r="L43" t="n">
-        <v>1168</v>
+        <v>1091.789678462916</v>
       </c>
       <c r="M43" t="n">
-        <v>1168</v>
+        <v>1091.789678462916</v>
       </c>
       <c r="N43" t="n">
-        <v>943.5810301113962</v>
+        <v>867.3707085743118</v>
       </c>
       <c r="O43" t="n">
-        <v>648.6315351619012</v>
+        <v>572.421213624558</v>
       </c>
       <c r="P43" t="n">
-        <v>353.6820402124062</v>
+        <v>277.4717186747975</v>
       </c>
       <c r="Q43" t="n">
-        <v>353.6820402124062</v>
+        <v>23.36</v>
       </c>
       <c r="R43" t="n">
-        <v>65.50953240394406</v>
+        <v>23.36</v>
       </c>
       <c r="S43" t="n">
         <v>23.36</v>
@@ -7615,22 +7615,22 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>869.4120530651505</v>
+        <v>287.6573032682762</v>
       </c>
       <c r="C44" t="n">
-        <v>691.1549033247526</v>
+        <v>287.6573032682762</v>
       </c>
       <c r="D44" t="n">
-        <v>552.4284833855104</v>
+        <v>287.6573032682762</v>
       </c>
       <c r="E44" t="n">
-        <v>419.7382918634209</v>
+        <v>154.9671117461866</v>
       </c>
       <c r="F44" t="n">
-        <v>286.5164446836109</v>
+        <v>154.9671117461866</v>
       </c>
       <c r="G44" t="n">
-        <v>154.9093329374243</v>
+        <v>23.36</v>
       </c>
       <c r="H44" t="n">
         <v>23.36</v>
@@ -7639,25 +7639,25 @@
         <v>23.36</v>
       </c>
       <c r="J44" t="n">
-        <v>27.850947234446</v>
+        <v>312.4400000000541</v>
       </c>
       <c r="K44" t="n">
-        <v>86.57689155605404</v>
+        <v>371.1659443216622</v>
       </c>
       <c r="L44" t="n">
-        <v>226.4151738864654</v>
+        <v>444.020671155833</v>
       </c>
       <c r="M44" t="n">
-        <v>515.4951738864654</v>
+        <v>444.020671155833</v>
       </c>
       <c r="N44" t="n">
-        <v>804.5751738864653</v>
+        <v>589.8399999998919</v>
       </c>
       <c r="O44" t="n">
-        <v>812.815704817159</v>
+        <v>878.919999999946</v>
       </c>
       <c r="P44" t="n">
-        <v>878.9200000000001</v>
+        <v>1168</v>
       </c>
       <c r="Q44" t="n">
         <v>1168</v>
@@ -7666,25 +7666,25 @@
         <v>1168</v>
       </c>
       <c r="S44" t="n">
-        <v>1168</v>
+        <v>954.6448129909027</v>
       </c>
       <c r="T44" t="n">
-        <v>1168</v>
+        <v>954.6448129909027</v>
       </c>
       <c r="U44" t="n">
-        <v>1168</v>
+        <v>659.6953180413525</v>
       </c>
       <c r="V44" t="n">
-        <v>1168</v>
+        <v>659.6953180413525</v>
       </c>
       <c r="W44" t="n">
-        <v>1168</v>
+        <v>364.7458230918023</v>
       </c>
       <c r="X44" t="n">
-        <v>1168</v>
+        <v>364.7458230918023</v>
       </c>
       <c r="Y44" t="n">
-        <v>1080.522470191994</v>
+        <v>364.7458230918023</v>
       </c>
     </row>
     <row r="45">
@@ -7694,22 +7694,22 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>76.38022872834857</v>
+        <v>347.091721450426</v>
       </c>
       <c r="C45" t="n">
-        <v>76.38022872834857</v>
+        <v>347.091721450426</v>
       </c>
       <c r="D45" t="n">
-        <v>76.38022872834857</v>
+        <v>271.3970882204234</v>
       </c>
       <c r="E45" t="n">
-        <v>76.38022872834857</v>
+        <v>201.0212324407136</v>
       </c>
       <c r="F45" t="n">
-        <v>76.38022872834857</v>
+        <v>133.7118967458885</v>
       </c>
       <c r="G45" t="n">
-        <v>23.36</v>
+        <v>80.69166801753994</v>
       </c>
       <c r="H45" t="n">
         <v>23.36</v>
@@ -7718,19 +7718,19 @@
         <v>23.36</v>
       </c>
       <c r="J45" t="n">
-        <v>23.36</v>
+        <v>170.6539582885065</v>
       </c>
       <c r="K45" t="n">
-        <v>252.4402149623079</v>
+        <v>243.6470608192757</v>
       </c>
       <c r="L45" t="n">
-        <v>541.5202149623079</v>
+        <v>532.7270608193298</v>
       </c>
       <c r="M45" t="n">
-        <v>690.1885567051671</v>
+        <v>681.395402562189</v>
       </c>
       <c r="N45" t="n">
-        <v>887.7131541429241</v>
+        <v>878.919999999946</v>
       </c>
       <c r="O45" t="n">
         <v>1168</v>
@@ -7742,28 +7742,28 @@
         <v>1168</v>
       </c>
       <c r="R45" t="n">
-        <v>1060.013399922537</v>
+        <v>1027.203651928401</v>
       </c>
       <c r="S45" t="n">
-        <v>869.175549758169</v>
+        <v>1027.203651928401</v>
       </c>
       <c r="T45" t="n">
-        <v>736.4966940972536</v>
+        <v>894.5247962674858</v>
       </c>
       <c r="U45" t="n">
-        <v>608.0179621115493</v>
+        <v>766.0460642817817</v>
       </c>
       <c r="V45" t="n">
-        <v>465.0778942413269</v>
+        <v>623.1059964115593</v>
       </c>
       <c r="W45" t="n">
-        <v>465.0778942413269</v>
+        <v>623.1059964115593</v>
       </c>
       <c r="X45" t="n">
-        <v>316.7316927813395</v>
+        <v>474.7597949515718</v>
       </c>
       <c r="Y45" t="n">
-        <v>189.0636192801936</v>
+        <v>347.091721450426</v>
       </c>
     </row>
     <row r="46">
@@ -7773,19 +7773,19 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>323.1082709899421</v>
+        <v>323.108270989942</v>
       </c>
       <c r="C46" t="n">
-        <v>323.3802768083779</v>
+        <v>323.3802768083778</v>
       </c>
       <c r="D46" t="n">
         <v>310.7174302876147</v>
       </c>
       <c r="E46" t="n">
-        <v>302.6559102502849</v>
+        <v>302.6559102502848</v>
       </c>
       <c r="F46" t="n">
-        <v>302.6559102502849</v>
+        <v>302.6559102502848</v>
       </c>
       <c r="G46" t="n">
         <v>330.5395646617603</v>
@@ -7806,13 +7806,13 @@
         <v>615.8324393322446</v>
       </c>
       <c r="M46" t="n">
-        <v>398.8206775247344</v>
+        <v>398.8206775247343</v>
       </c>
       <c r="N46" t="n">
-        <v>129.9572631916862</v>
+        <v>129.9572631916861</v>
       </c>
       <c r="O46" t="n">
-        <v>23.36</v>
+        <v>129.9572631916861</v>
       </c>
       <c r="P46" t="n">
         <v>23.36</v>
@@ -7833,7 +7833,7 @@
         <v>207.4230003216817</v>
       </c>
       <c r="V46" t="n">
-        <v>280.5143932076277</v>
+        <v>280.5143932076276</v>
       </c>
       <c r="W46" t="n">
         <v>326.6753114673051</v>
@@ -7842,7 +7842,7 @@
         <v>351.9761024914986</v>
       </c>
       <c r="Y46" t="n">
-        <v>337.3646349667892</v>
+        <v>337.3646349667891</v>
       </c>
     </row>
   </sheetData>
@@ -7964,7 +7964,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J2" t="n">
-        <v>329.4636896621757</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -7979,13 +7979,13 @@
         <v>728.0402344517447</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>325.6762313831376</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>234.9636091709278</v>
+        <v>238.7510674499657</v>
       </c>
       <c r="R2" t="n">
         <v>294.54111633436</v>
@@ -8046,10 +8046,10 @@
         <v>227.4647419277884</v>
       </c>
       <c r="K3" t="n">
-        <v>259.4311994555707</v>
+        <v>295.8802408630135</v>
       </c>
       <c r="L3" t="n">
-        <v>388.0893364597981</v>
+        <v>190.328932047136</v>
       </c>
       <c r="M3" t="n">
         <v>471.6948204301074</v>
@@ -8061,7 +8061,7 @@
         <v>382.6817988009037</v>
       </c>
       <c r="P3" t="n">
-        <v>57.83934883533021</v>
+        <v>219.1507118405495</v>
       </c>
       <c r="Q3" t="n">
         <v>17.27519534353338</v>
@@ -8207,7 +8207,7 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>107.9631873699396</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
         <v>796.3783688483475</v>
@@ -8216,13 +8216,13 @@
         <v>728.0402344517447</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>174.7352027061427</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>267.227984663797</v>
       </c>
       <c r="Q5" t="n">
-        <v>456.4641114631638</v>
+        <v>122.4641114631638</v>
       </c>
       <c r="R5" t="n">
         <v>294.54111633436</v>
@@ -8286,7 +8286,7 @@
         <v>295.8802408630135</v>
       </c>
       <c r="L6" t="n">
-        <v>190.328932047136</v>
+        <v>351.6402950523553</v>
       </c>
       <c r="M6" t="n">
         <v>471.6948204301074</v>
@@ -8298,7 +8298,7 @@
         <v>382.6817988009037</v>
       </c>
       <c r="P6" t="n">
-        <v>219.1507118405495</v>
+        <v>57.83934883533021</v>
       </c>
       <c r="Q6" t="n">
         <v>17.27519534353338</v>
@@ -8444,13 +8444,13 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>129.0742984810493</v>
+        <v>129.0742984810508</v>
       </c>
       <c r="M8" t="n">
-        <v>818.378368848348</v>
+        <v>818.3783688483475</v>
       </c>
       <c r="N8" t="n">
-        <v>750.0402344517452</v>
+        <v>750.0402344517447</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -8459,7 +8459,7 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>478.4641114631643</v>
+        <v>478.4641114631638</v>
       </c>
       <c r="R8" t="n">
         <v>294.54111633436</v>
@@ -8523,7 +8523,7 @@
         <v>295.8802408630135</v>
       </c>
       <c r="L9" t="n">
-        <v>277.4400431582471</v>
+        <v>388.0893364597981</v>
       </c>
       <c r="M9" t="n">
         <v>471.6948204301074</v>
@@ -8535,7 +8535,7 @@
         <v>382.6817988009037</v>
       </c>
       <c r="P9" t="n">
-        <v>219.1507118405495</v>
+        <v>108.5014185389983</v>
       </c>
       <c r="Q9" t="n">
         <v>17.27519534353338</v>
@@ -8675,19 +8675,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>363.4636896621757</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>140.5894499962003</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>830.3783688483483</v>
+        <v>830.3783688483475</v>
       </c>
       <c r="N11" t="n">
-        <v>762.0402344517454</v>
+        <v>762.0402344517447</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -8696,7 +8696,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>490.4641114631646</v>
+        <v>267.5898717971906</v>
       </c>
       <c r="R11" t="n">
         <v>294.54111633436</v>
@@ -8760,7 +8760,7 @@
         <v>295.8802408630135</v>
       </c>
       <c r="L12" t="n">
-        <v>388.0893364597981</v>
+        <v>324.9551946733986</v>
       </c>
       <c r="M12" t="n">
         <v>471.6948204301074</v>
@@ -8769,7 +8769,7 @@
         <v>485.4085271713503</v>
       </c>
       <c r="O12" t="n">
-        <v>319.5476570145042</v>
+        <v>382.6817988009037</v>
       </c>
       <c r="P12" t="n">
         <v>219.1507118405495</v>
@@ -8912,19 +8912,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J14" t="n">
-        <v>363.4636896621765</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>140.5894499962025</v>
       </c>
       <c r="M14" t="n">
-        <v>607.504129182372</v>
+        <v>830.3783688483475</v>
       </c>
       <c r="N14" t="n">
-        <v>762.0402344517454</v>
+        <v>762.0402344517447</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -8933,7 +8933,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>490.4641114631646</v>
+        <v>490.4641114631638</v>
       </c>
       <c r="R14" t="n">
         <v>294.54111633436</v>
@@ -9006,10 +9006,10 @@
         <v>485.4085271713503</v>
       </c>
       <c r="O15" t="n">
-        <v>319.5476570145042</v>
+        <v>382.6817988009037</v>
       </c>
       <c r="P15" t="n">
-        <v>219.1507118405495</v>
+        <v>156.01657005415</v>
       </c>
       <c r="Q15" t="n">
         <v>17.27519534353338</v>
@@ -9149,19 +9149,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J17" t="n">
-        <v>363.4636896621765</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>140.5894499962025</v>
       </c>
       <c r="M17" t="n">
-        <v>830.3783688483483</v>
+        <v>830.3783688483475</v>
       </c>
       <c r="N17" t="n">
-        <v>762.0402344517454</v>
+        <v>762.0402344517447</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -9170,7 +9170,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>267.5898717971881</v>
+        <v>490.4641114631638</v>
       </c>
       <c r="R17" t="n">
         <v>294.54111633436</v>
@@ -9243,10 +9243,10 @@
         <v>485.4085271713503</v>
       </c>
       <c r="O18" t="n">
-        <v>382.6817988009037</v>
+        <v>319.5476570145042</v>
       </c>
       <c r="P18" t="n">
-        <v>156.01657005415</v>
+        <v>219.1507118405495</v>
       </c>
       <c r="Q18" t="n">
         <v>17.27519534353338</v>
@@ -9386,7 +9386,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J20" t="n">
-        <v>363.4636896621765</v>
+        <v>363.4636896621757</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -9395,10 +9395,10 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>607.504129182372</v>
+        <v>607.5041291823743</v>
       </c>
       <c r="N20" t="n">
-        <v>762.0402344517454</v>
+        <v>762.0402344517447</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -9407,7 +9407,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>490.4641114631646</v>
+        <v>490.4641114631638</v>
       </c>
       <c r="R20" t="n">
         <v>294.54111633436</v>
@@ -9471,7 +9471,7 @@
         <v>295.8802408630135</v>
       </c>
       <c r="L21" t="n">
-        <v>324.9551946733986</v>
+        <v>388.0893364597981</v>
       </c>
       <c r="M21" t="n">
         <v>471.6948204301074</v>
@@ -9480,7 +9480,7 @@
         <v>485.4085271713503</v>
       </c>
       <c r="O21" t="n">
-        <v>382.6817988009037</v>
+        <v>319.5476570145042</v>
       </c>
       <c r="P21" t="n">
         <v>219.1507118405495</v>
@@ -9626,22 +9626,22 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>140.5894499962003</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>462.3783688483475</v>
+        <v>830.3783688483483</v>
       </c>
       <c r="N23" t="n">
-        <v>609.7254684010104</v>
+        <v>762.0402344517454</v>
       </c>
       <c r="O23" t="n">
-        <v>359.6762313831384</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>301.2279846637977</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
         <v>490.4641114631646</v>
@@ -9717,10 +9717,10 @@
         <v>485.4085271713503</v>
       </c>
       <c r="O24" t="n">
-        <v>319.5476570145042</v>
+        <v>382.6817988009037</v>
       </c>
       <c r="P24" t="n">
-        <v>219.1507118405495</v>
+        <v>156.01657005415</v>
       </c>
       <c r="Q24" t="n">
         <v>17.27519534353338</v>
@@ -9860,13 +9860,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J26" t="n">
-        <v>321.4636896621757</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>100.286419693172</v>
       </c>
       <c r="M26" t="n">
         <v>788.3783688483475</v>
@@ -9881,7 +9881,7 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>227.28684149416</v>
+        <v>448.4641114631638</v>
       </c>
       <c r="R26" t="n">
         <v>294.54111633436</v>
@@ -9939,13 +9939,13 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J27" t="n">
-        <v>227.4647419277884</v>
+        <v>78.68296587879195</v>
       </c>
       <c r="K27" t="n">
-        <v>68.70972714113864</v>
+        <v>295.8802408630135</v>
       </c>
       <c r="L27" t="n">
-        <v>385.8226780922432</v>
+        <v>307.4339404193648</v>
       </c>
       <c r="M27" t="n">
         <v>471.6948204301074</v>
@@ -10334,19 +10334,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>299.4636896621776</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>230.4093668341709</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>615.1443105962338</v>
+        <v>766.3783688483494</v>
       </c>
       <c r="N32" t="n">
-        <v>698.0402344517465</v>
+        <v>477.7518533716243</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -10416,7 +10416,7 @@
         <v>78.68296587879195</v>
       </c>
       <c r="K33" t="n">
-        <v>152.3803920790222</v>
+        <v>295.8802408630135</v>
       </c>
       <c r="L33" t="n">
         <v>363.822678092245</v>
@@ -10431,7 +10431,7 @@
         <v>382.6817988009037</v>
       </c>
       <c r="P33" t="n">
-        <v>219.1507118405495</v>
+        <v>75.65086305655808</v>
       </c>
       <c r="Q33" t="n">
         <v>17.27519534353338</v>
@@ -10577,22 +10577,22 @@
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>67.66015706690966</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>754.3783688483475</v>
+        <v>754.3783688483549</v>
       </c>
       <c r="N35" t="n">
-        <v>686.0402344517447</v>
+        <v>686.0402344517522</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>283.6762313831451</v>
       </c>
       <c r="P35" t="n">
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>414.4641114631638</v>
+        <v>198.4480371469133</v>
       </c>
       <c r="R35" t="n">
         <v>294.54111633436</v>
@@ -10656,19 +10656,19 @@
         <v>295.8802408630135</v>
       </c>
       <c r="L36" t="n">
-        <v>194.1589281615053</v>
+        <v>351.8226780922506</v>
       </c>
       <c r="M36" t="n">
-        <v>471.6948204301074</v>
+        <v>321.5247782656032</v>
       </c>
       <c r="N36" t="n">
         <v>485.4085271713503</v>
       </c>
       <c r="O36" t="n">
-        <v>373.8601353887233</v>
+        <v>205.055064617263</v>
       </c>
       <c r="P36" t="n">
-        <v>57.83934883533021</v>
+        <v>219.1507118405495</v>
       </c>
       <c r="Q36" t="n">
         <v>17.27519534353338</v>
@@ -10811,16 +10811,16 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>232.6808643216081</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>67.66015706686561</v>
       </c>
       <c r="M38" t="n">
-        <v>754.3783688483475</v>
+        <v>754.3783688483621</v>
       </c>
       <c r="N38" t="n">
-        <v>686.0402344517447</v>
+        <v>686.0402344517593</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -10829,7 +10829,7 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>249.4434042084652</v>
+        <v>414.4641114631784</v>
       </c>
       <c r="R38" t="n">
         <v>294.54111633436</v>
@@ -10893,7 +10893,7 @@
         <v>295.8802408630135</v>
       </c>
       <c r="L39" t="n">
-        <v>324.847565156286</v>
+        <v>351.8226780922578</v>
       </c>
       <c r="M39" t="n">
         <v>471.6948204301074</v>
@@ -10902,10 +10902,10 @@
         <v>485.4085271713503</v>
       </c>
       <c r="O39" t="n">
-        <v>81.86013538872336</v>
+        <v>216.1963854579709</v>
       </c>
       <c r="P39" t="n">
-        <v>219.1507118405495</v>
+        <v>57.83934883533021</v>
       </c>
       <c r="Q39" t="n">
         <v>17.27519534353338</v>
@@ -11045,28 +11045,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>149.5745588495531</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>67.66015706690966</v>
+        <v>218.4093668341708</v>
       </c>
       <c r="M41" t="n">
-        <v>754.3783688483475</v>
+        <v>462.3783688483475</v>
       </c>
       <c r="N41" t="n">
-        <v>686.0402344517447</v>
+        <v>686.0402344517686</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>283.6762313831616</v>
       </c>
       <c r="P41" t="n">
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>414.4641114631638</v>
+        <v>122.4641114631638</v>
       </c>
       <c r="R41" t="n">
         <v>294.54111633436</v>
@@ -11127,10 +11127,10 @@
         <v>227.4647419277884</v>
       </c>
       <c r="K42" t="n">
-        <v>138.2164909322757</v>
+        <v>64.48608433542975</v>
       </c>
       <c r="L42" t="n">
-        <v>351.8226780922432</v>
+        <v>264.2417216838459</v>
       </c>
       <c r="M42" t="n">
         <v>471.6948204301074</v>
@@ -11139,10 +11139,10 @@
         <v>485.4085271713503</v>
       </c>
       <c r="O42" t="n">
-        <v>373.8601353887233</v>
+        <v>373.8601353887473</v>
       </c>
       <c r="P42" t="n">
-        <v>57.83934883533021</v>
+        <v>219.1507118405495</v>
       </c>
       <c r="Q42" t="n">
         <v>17.27519534353338</v>
@@ -11282,28 +11282,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>287.4636896622304</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>67.66015706690966</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>754.3783688483475</v>
+        <v>462.3783688483475</v>
       </c>
       <c r="N44" t="n">
-        <v>686.0402344517447</v>
+        <v>541.3324858093799</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>283.6762313831923</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>225.2279846638516</v>
       </c>
       <c r="Q44" t="n">
-        <v>414.4641114631638</v>
+        <v>122.4641114631638</v>
       </c>
       <c r="R44" t="n">
         <v>294.54111633436</v>
@@ -11361,13 +11361,13 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J45" t="n">
-        <v>78.68296587879195</v>
+        <v>227.4647419277884</v>
       </c>
       <c r="K45" t="n">
-        <v>295.8802408630135</v>
+        <v>138.2164909321664</v>
       </c>
       <c r="L45" t="n">
-        <v>351.8226780922432</v>
+        <v>351.8226780922978</v>
       </c>
       <c r="M45" t="n">
         <v>471.6948204301074</v>
@@ -11376,7 +11376,7 @@
         <v>485.4085271713503</v>
       </c>
       <c r="O45" t="n">
-        <v>364.9781615069819</v>
+        <v>373.860135388778</v>
       </c>
       <c r="P45" t="n">
         <v>57.83934883533021</v>
@@ -22512,10 +22512,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>76.99931295557451</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>8.490140323435867</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -22578,7 +22578,7 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>85.48945327901039</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -22800,10 +22800,10 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>79.22163513900631</v>
       </c>
       <c r="T5" t="n">
-        <v>85.48945327901048</v>
+        <v>6.267818140004266</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -23223,7 +23223,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>162.9993129555745</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
@@ -23238,10 +23238,10 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>84.29104062872476</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>84.23383960805002</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -23274,7 +23274,7 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>165.2216351390063</v>
       </c>
       <c r="T11" t="n">
         <v>265.634214894393</v>
@@ -23283,16 +23283,16 @@
         <v>330.1839900159474</v>
       </c>
       <c r="V11" t="n">
-        <v>310.8510241668239</v>
+        <v>36.96346614293805</v>
       </c>
       <c r="W11" t="n">
-        <v>78.12594251672675</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>192.3174326828064</v>
       </c>
     </row>
     <row r="12">
@@ -23411,19 +23411,19 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>73.4482183217136</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>114.6419181724533</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>291.8788755544248</v>
       </c>
       <c r="P13" t="n">
-        <v>333.0725754051645</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
         <v>21.323266425598</v>
@@ -23460,25 +23460,25 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>118.9993129555745</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>86.47457824299391</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>47.33915573984979</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>41.36328960686865</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>41.88962870801186</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>40.29104062872477</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>40.23383960805</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -23511,22 +23511,22 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>121.2216351390063</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>221.634214894393</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>194.4642017972662</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>120.7292063405922</v>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
@@ -23648,7 +23648,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>29.44821832171363</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -23663,10 +23663,10 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>119.4292736358173</v>
       </c>
       <c r="R16" t="n">
-        <v>148.8774919575309</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -23748,7 +23748,7 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>5.320051830665776</v>
       </c>
       <c r="T17" t="n">
         <v>0</v>
@@ -23760,7 +23760,7 @@
         <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>5.320051830665591</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -23991,7 +23991,7 @@
         <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>5.320051830665705</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -24003,7 +24003,7 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>5.320051830665719</v>
       </c>
     </row>
     <row r="21">
@@ -24222,7 +24222,7 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>5.320051830665761</v>
+        <v>5.320051830665776</v>
       </c>
       <c r="T23" t="n">
         <v>0</v>
@@ -24408,10 +24408,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>172.9993129555745</v>
+        <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>140.4745782429939</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
         <v>101.3391557398498</v>
@@ -24420,13 +24420,13 @@
         <v>95.36328960686865</v>
       </c>
       <c r="F26" t="n">
-        <v>95.88962870801186</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
         <v>94.29104062872476</v>
       </c>
       <c r="H26" t="n">
-        <v>94.23383960805002</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -24465,19 +24465,19 @@
         <v>275.634214894393</v>
       </c>
       <c r="U26" t="n">
-        <v>14.18399001594735</v>
+        <v>187.9223829912632</v>
       </c>
       <c r="V26" t="n">
-        <v>193.3094903102981</v>
+        <v>320.8510241668239</v>
       </c>
       <c r="W26" t="n">
-        <v>3.373475980947546</v>
+        <v>3.373475980929811</v>
       </c>
       <c r="X26" t="n">
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>202.3174326828064</v>
       </c>
     </row>
     <row r="27">
@@ -24596,7 +24596,7 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>83.4482183217136</v>
       </c>
       <c r="M28" t="n">
         <v>178.8416441894351</v>
@@ -24605,19 +24605,19 @@
         <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>301.8788755544248</v>
+        <v>294.6408928241445</v>
       </c>
       <c r="P28" t="n">
-        <v>27.1484874922119</v>
+        <v>27.14848749217708</v>
       </c>
       <c r="Q28" t="n">
-        <v>99.80546493702934</v>
+        <v>73.323266425567</v>
       </c>
       <c r="R28" t="n">
-        <v>82.19661978442974</v>
+        <v>82.19661978439808</v>
       </c>
       <c r="S28" t="n">
-        <v>49.72803707990462</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
@@ -24654,7 +24654,7 @@
         <v>101.3391557398498</v>
       </c>
       <c r="E29" t="n">
-        <v>37.12223761287231</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -24663,7 +24663,7 @@
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>94.23383960805002</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -24699,7 +24699,7 @@
         <v>175.2216351390063</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>275.634214894393</v>
       </c>
       <c r="U29" t="n">
         <v>14.18399001594735</v>
@@ -24708,10 +24708,10 @@
         <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>329.3734759809475</v>
+        <v>3.373475980947546</v>
       </c>
       <c r="X29" t="n">
-        <v>283.2818334606677</v>
+        <v>276.536016571097</v>
       </c>
       <c r="Y29" t="n">
         <v>202.3174326828064</v>
@@ -24842,19 +24842,19 @@
         <v>230.1747801897177</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>64.46611263432939</v>
       </c>
       <c r="P31" t="n">
         <v>27.1484874922119</v>
       </c>
       <c r="Q31" t="n">
-        <v>88.06134198002275</v>
+        <v>73.32326642559801</v>
       </c>
       <c r="R31" t="n">
         <v>82.19661978442974</v>
       </c>
       <c r="S31" t="n">
-        <v>49.72803707990462</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
         <v>0</v>
@@ -25182,13 +25182,13 @@
         <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>0.1438975391606334</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>0.1438975391607613</v>
       </c>
     </row>
     <row r="36">
@@ -25310,13 +25310,13 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>0.370073635817306</v>
       </c>
       <c r="N37" t="n">
         <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>0.3700736358174481</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
         <v>0</v>
@@ -25407,7 +25407,7 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>0.1438975391606796</v>
       </c>
       <c r="T38" t="n">
         <v>0</v>
@@ -25419,7 +25419,7 @@
         <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>0.1438975391606334</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
         <v>0</v>
@@ -25547,13 +25547,13 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>0.370073635817306</v>
       </c>
       <c r="N40" t="n">
         <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>0.3700736358174481</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
         <v>0</v>
@@ -25593,22 +25593,22 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>164.9993129555745</v>
+        <v>0</v>
       </c>
       <c r="C41" t="n">
-        <v>132.4745782429939</v>
+        <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>93.33915573984979</v>
+        <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>87.36328960686865</v>
+        <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>87.88962870801186</v>
+        <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>86.29104062872476</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
         <v>86.23383960805002</v>
@@ -25647,22 +25647,22 @@
         <v>167.2216351390063</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>267.634214894393</v>
       </c>
       <c r="U41" t="n">
-        <v>50.62460491034051</v>
+        <v>332.1839900159474</v>
       </c>
       <c r="V41" t="n">
-        <v>20.85102416682389</v>
+        <v>312.8510241668239</v>
       </c>
       <c r="W41" t="n">
-        <v>29.37347598094755</v>
+        <v>310.1361480064454</v>
       </c>
       <c r="X41" t="n">
-        <v>275.2818334606677</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>194.3174326828064</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -25781,7 +25781,7 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>75.4482183217136</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
         <v>170.8416441894351</v>
@@ -25790,19 +25790,19 @@
         <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>1.878875554424784</v>
+        <v>1.87887555416853</v>
       </c>
       <c r="P43" t="n">
-        <v>53.1484874922119</v>
+        <v>53.14848749194903</v>
       </c>
       <c r="Q43" t="n">
-        <v>391.323266425598</v>
+        <v>139.7526649375485</v>
       </c>
       <c r="R43" t="n">
-        <v>114.9058370540523</v>
+        <v>400.1966197844297</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>41.72803707990462</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
@@ -25830,25 +25830,25 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0</v>
+        <v>132.6816783302836</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>176.4745782429939</v>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>137.3391557398498</v>
       </c>
       <c r="E44" t="n">
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>131.8896287080119</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>130.23383960805</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -25881,25 +25881,25 @@
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>211.2216351390063</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
         <v>311.634214894393</v>
       </c>
       <c r="U44" t="n">
-        <v>376.1839900159473</v>
+        <v>84.18399001589266</v>
       </c>
       <c r="V44" t="n">
         <v>356.8510241668239</v>
       </c>
       <c r="W44" t="n">
-        <v>365.3734759809475</v>
+        <v>73.37347598089292</v>
       </c>
       <c r="X44" t="n">
         <v>319.2818334606677</v>
       </c>
       <c r="Y44" t="n">
-        <v>151.71467817288</v>
+        <v>238.3174326828064</v>
       </c>
     </row>
     <row r="45">
@@ -25909,25 +25909,25 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0</v>
+        <v>111.5565566463266</v>
       </c>
       <c r="C45" t="n">
         <v>88.09991244551929</v>
       </c>
       <c r="D45" t="n">
-        <v>74.93768689770263</v>
+        <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>69.67209722191262</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>66.63624233787687</v>
+        <v>0</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>56.7583513373645</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
@@ -25957,10 +25957,10 @@
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>151.875591517578</v>
+        <v>119.3939410033834</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>188.9294716627245</v>
       </c>
       <c r="T45" t="n">
         <v>0</v>
@@ -26027,19 +26027,19 @@
         <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>232.3475849946554</v>
+        <v>337.8788755544248</v>
       </c>
       <c r="P46" t="n">
-        <v>389.1484874922119</v>
+        <v>283.6171969324427</v>
       </c>
       <c r="Q46" t="n">
         <v>435.323266425598</v>
       </c>
       <c r="R46" t="n">
-        <v>444.1966197844298</v>
+        <v>444.1966197844297</v>
       </c>
       <c r="S46" t="n">
-        <v>85.7280370799046</v>
+        <v>85.72803707990461</v>
       </c>
       <c r="T46" t="n">
         <v>0</v>
@@ -26086,7 +26086,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>949586.3019733871</v>
+        <v>949586.3019733874</v>
       </c>
     </row>
     <row r="3">
@@ -26110,7 +26110,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3340895.529371636</v>
+        <v>3340895.529371637</v>
       </c>
     </row>
     <row r="6">
@@ -26118,7 +26118,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>4129367.177231567</v>
+        <v>4129367.177231568</v>
       </c>
     </row>
     <row r="7">
@@ -26126,7 +26126,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4947686.993966033</v>
+        <v>4947686.993966035</v>
       </c>
     </row>
     <row r="8">
@@ -26134,7 +26134,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5766006.810700497</v>
+        <v>5766006.810700499</v>
       </c>
     </row>
     <row r="9">
@@ -26142,7 +26142,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6584326.627434961</v>
+        <v>6584326.627434963</v>
       </c>
     </row>
     <row r="10">
@@ -26150,7 +26150,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7306904.252528806</v>
+        <v>7306904.252528809</v>
       </c>
     </row>
     <row r="11">
@@ -26158,7 +26158,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8038611.913986284</v>
+        <v>8038611.913986287</v>
       </c>
     </row>
     <row r="12">
@@ -26166,7 +26166,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>8852424.590202468</v>
+        <v>8852424.590202471</v>
       </c>
     </row>
     <row r="13">
@@ -26174,7 +26174,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9668397.866193084</v>
+        <v>9668397.866193088</v>
       </c>
     </row>
     <row r="14">
@@ -26269,28 +26269,28 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>1377829.287836744</v>
+      </c>
+      <c r="C2" t="n">
         <v>1377829.287836745</v>
       </c>
-      <c r="C2" t="n">
-        <v>1377829.287836744</v>
-      </c>
       <c r="D2" t="n">
-        <v>1385304.950492745</v>
+        <v>1385304.950492744</v>
       </c>
       <c r="E2" t="n">
         <v>1271188.946498318</v>
       </c>
       <c r="F2" t="n">
-        <v>1334336.634839884</v>
+        <v>1334336.634839881</v>
       </c>
       <c r="G2" t="n">
-        <v>1384848.920627561</v>
+        <v>1384848.920627563</v>
       </c>
       <c r="H2" t="n">
+        <v>1384848.920627562</v>
+      </c>
+      <c r="I2" t="n">
         <v>1384848.920627563</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1384848.920627562</v>
       </c>
       <c r="J2" t="n">
         <v>1238274.504004973</v>
@@ -26299,19 +26299,19 @@
         <v>1238274.504004973</v>
       </c>
       <c r="L2" t="n">
-        <v>1385314.744365855</v>
+        <v>1385314.744365854</v>
       </c>
       <c r="M2" t="n">
         <v>1385292.374753341</v>
       </c>
       <c r="N2" t="n">
-        <v>1385292.37475334</v>
+        <v>1385292.374753341</v>
       </c>
       <c r="O2" t="n">
         <v>1234391.176022468</v>
       </c>
       <c r="P2" t="n">
-        <v>1129064.490222999</v>
+        <v>1129064.490223</v>
       </c>
     </row>
     <row r="3">
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>645802.4527138101</v>
+        <v>645788.5882818315</v>
       </c>
       <c r="C4" t="n">
-        <v>643769.7373577412</v>
+        <v>643755.8729257626</v>
       </c>
       <c r="D4" t="n">
-        <v>644590.781093542</v>
+        <v>644576.4270147089</v>
       </c>
       <c r="E4" t="n">
-        <v>583345.4427368056</v>
+        <v>583330.8215778702</v>
       </c>
       <c r="F4" t="n">
-        <v>613927.0182820035</v>
+        <v>613912.3971230681</v>
       </c>
       <c r="G4" t="n">
-        <v>637758.0284239212</v>
+        <v>637743.4072649858</v>
       </c>
       <c r="H4" t="n">
-        <v>635733.7812118242</v>
+        <v>635719.1600528888</v>
       </c>
       <c r="I4" t="n">
-        <v>633706.7081177637</v>
+        <v>633692.0869588284</v>
       </c>
       <c r="J4" t="n">
-        <v>559422.9725505344</v>
+        <v>559409.2861719572</v>
       </c>
       <c r="K4" t="n">
-        <v>557653.6393873302</v>
+        <v>557639.9530087529</v>
       </c>
       <c r="L4" t="n">
-        <v>630158.6576315102</v>
+        <v>630145.4608997871</v>
       </c>
       <c r="M4" t="n">
-        <v>628458.5130951514</v>
+        <v>628445.5834435306</v>
       </c>
       <c r="N4" t="n">
-        <v>626332.3070036485</v>
+        <v>626319.3773520278</v>
       </c>
       <c r="O4" t="n">
-        <v>549738.6829049777</v>
+        <v>549725.753253357</v>
       </c>
       <c r="P4" t="n">
-        <v>496062.9880861851</v>
+        <v>496050.0584345643</v>
       </c>
     </row>
     <row r="5">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>440474.8901229348</v>
+        <v>440488.754554913</v>
       </c>
       <c r="C6" t="n">
-        <v>677175.6054790032</v>
+        <v>677189.4699109821</v>
       </c>
       <c r="D6" t="n">
-        <v>674748.6243992028</v>
+        <v>674762.9784780352</v>
       </c>
       <c r="E6" t="n">
-        <v>380698.2927615124</v>
+        <v>380712.9139204479</v>
       </c>
       <c r="F6" t="n">
-        <v>629789.3695578803</v>
+        <v>629803.9907168134</v>
       </c>
       <c r="G6" t="n">
-        <v>654076.0232036402</v>
+        <v>654090.6443625768</v>
       </c>
       <c r="H6" t="n">
-        <v>690500.2704157392</v>
+        <v>690514.8915746731</v>
       </c>
       <c r="I6" t="n">
-        <v>692527.3435097984</v>
+        <v>692541.9646687345</v>
       </c>
       <c r="J6" t="n">
-        <v>350140.6104544391</v>
+        <v>350154.2968330159</v>
       </c>
       <c r="K6" t="n">
-        <v>597093.9436176433</v>
+        <v>597107.6299962206</v>
       </c>
       <c r="L6" t="n">
-        <v>569446.6237343452</v>
+        <v>569459.8204660673</v>
       </c>
       <c r="M6" t="n">
-        <v>696233.6536581897</v>
+        <v>696246.58330981</v>
       </c>
       <c r="N6" t="n">
-        <v>702359.8597496919</v>
+        <v>702372.7894013131</v>
       </c>
       <c r="O6" t="n">
-        <v>552120.2201174906</v>
+        <v>552133.1497691113</v>
       </c>
       <c r="P6" t="n">
-        <v>589768.2651368139</v>
+        <v>589781.1947884355</v>
       </c>
     </row>
   </sheetData>
@@ -27008,7 +27008,7 @@
         <v>5</v>
       </c>
       <c r="N2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
         <v>107</v>
@@ -27524,7 +27524,7 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F3" t="n">
-        <v>5.636242337876865</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G3" t="n">
         <v>325.4900264410651</v>
@@ -27533,7 +27533,7 @@
         <v>329.7583513373645</v>
       </c>
       <c r="I3" t="n">
-        <v>208.5358198536127</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -27557,13 +27557,13 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>40.26486916163203</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>405</v>
+        <v>197.7823255942661</v>
       </c>
       <c r="S3" t="n">
-        <v>405</v>
+        <v>127.9294716627245</v>
       </c>
       <c r="T3" t="n">
         <v>404.3520671043063</v>
@@ -27575,10 +27575,10 @@
         <v>405</v>
       </c>
       <c r="W3" t="n">
-        <v>98.37314290982852</v>
+        <v>405</v>
       </c>
       <c r="X3" t="n">
-        <v>85.86273944538755</v>
+        <v>178.3247741134702</v>
       </c>
       <c r="Y3" t="n">
         <v>399.3913927661343</v>
@@ -27591,10 +27591,10 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>330.090816264371</v>
+      </c>
+      <c r="C4" t="n">
         <v>405</v>
-      </c>
-      <c r="C4" t="n">
-        <v>330.090816264371</v>
       </c>
       <c r="D4" t="n">
         <v>405</v>
@@ -27764,7 +27764,7 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G6" t="n">
-        <v>325.4900264410651</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>329.7583513373645</v>
@@ -27800,7 +27800,7 @@
         <v>197.7823255942661</v>
       </c>
       <c r="S6" t="n">
-        <v>127.9294716627245</v>
+        <v>226.7442722172596</v>
       </c>
       <c r="T6" t="n">
         <v>404.3520671043063</v>
@@ -27812,7 +27812,7 @@
         <v>405</v>
       </c>
       <c r="W6" t="n">
-        <v>178.3247741134701</v>
+        <v>405</v>
       </c>
       <c r="X6" t="n">
         <v>405</v>
@@ -27828,10 +27828,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>405</v>
+        <v>287.1138003370787</v>
       </c>
       <c r="C7" t="n">
-        <v>405</v>
+        <v>272.7252466480447</v>
       </c>
       <c r="D7" t="n">
         <v>405</v>
@@ -27843,22 +27843,22 @@
         <v>405</v>
       </c>
       <c r="G7" t="n">
-        <v>282.894700723549</v>
+        <v>405</v>
       </c>
       <c r="H7" t="n">
-        <v>226.9113228229301</v>
+        <v>405</v>
       </c>
       <c r="I7" t="n">
-        <v>170.3428326692986</v>
+        <v>405</v>
       </c>
       <c r="J7" t="n">
-        <v>20.47989965557989</v>
+        <v>354.4798996555799</v>
       </c>
       <c r="K7" t="n">
-        <v>264.2178229814709</v>
+        <v>292.5237321993433</v>
       </c>
       <c r="L7" t="n">
-        <v>392.4482183217136</v>
+        <v>405</v>
       </c>
       <c r="M7" t="n">
         <v>405</v>
@@ -27888,16 +27888,16 @@
         <v>150.9469814383924</v>
       </c>
       <c r="V7" t="n">
-        <v>405</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W7" t="n">
-        <v>405</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X7" t="n">
-        <v>405</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y7" t="n">
-        <v>405</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="8">
@@ -27986,16 +27986,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>28.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C9" t="n">
-        <v>361.0999124455193</v>
+        <v>5.099912445519294</v>
       </c>
       <c r="D9" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F9" t="n">
         <v>339.6362423378769</v>
@@ -28052,7 +28052,7 @@
         <v>405</v>
       </c>
       <c r="X9" t="n">
-        <v>98.79524873876079</v>
+        <v>104.0608384145508</v>
       </c>
       <c r="Y9" t="n">
         <v>399.3913927661343</v>
@@ -28065,7 +28065,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>287.1138003370787</v>
+        <v>405</v>
       </c>
       <c r="C10" t="n">
         <v>405</v>
@@ -28080,16 +28080,16 @@
         <v>405</v>
       </c>
       <c r="G10" t="n">
-        <v>405</v>
+        <v>244.8346925136612</v>
       </c>
       <c r="H10" t="n">
-        <v>405</v>
+        <v>226.9113228229301</v>
       </c>
       <c r="I10" t="n">
-        <v>405</v>
+        <v>170.3428326692986</v>
       </c>
       <c r="J10" t="n">
-        <v>263.0628371997828</v>
+        <v>20.47989965557989</v>
       </c>
       <c r="K10" t="n">
         <v>264.2178229814709</v>
@@ -28122,19 +28122,19 @@
         <v>209.1307960144544</v>
       </c>
       <c r="U10" t="n">
-        <v>150.9469814383924</v>
+        <v>189.0069896482801</v>
       </c>
       <c r="V10" t="n">
-        <v>199.1703102162162</v>
+        <v>405</v>
       </c>
       <c r="W10" t="n">
-        <v>226.3728098387097</v>
+        <v>405</v>
       </c>
       <c r="X10" t="n">
-        <v>247.4436454301076</v>
+        <v>405</v>
       </c>
       <c r="Y10" t="n">
-        <v>287.4653528494624</v>
+        <v>405</v>
       </c>
     </row>
     <row r="11">
@@ -28244,7 +28244,7 @@
         <v>319</v>
       </c>
       <c r="I12" t="n">
-        <v>208.5358198536127</v>
+        <v>32.17764923451621</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -28283,7 +28283,7 @@
         <v>319</v>
       </c>
       <c r="V12" t="n">
-        <v>142.6418293809035</v>
+        <v>319</v>
       </c>
       <c r="W12" t="n">
         <v>319</v>
@@ -28463,7 +28463,7 @@
         <v>363</v>
       </c>
       <c r="C15" t="n">
-        <v>343.5684072619189</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D15" t="n">
         <v>347.9376868977026</v>
@@ -28508,7 +28508,7 @@
         <v>141.2296047131211</v>
       </c>
       <c r="R15" t="n">
-        <v>163.7823255942661</v>
+        <v>363</v>
       </c>
       <c r="S15" t="n">
         <v>363</v>
@@ -28517,19 +28517,19 @@
         <v>363</v>
       </c>
       <c r="U15" t="n">
-        <v>32.19394466584713</v>
+        <v>159.5637757748195</v>
       </c>
       <c r="V15" t="n">
         <v>363</v>
       </c>
       <c r="W15" t="n">
-        <v>64.37314290982852</v>
+        <v>363</v>
       </c>
       <c r="X15" t="n">
-        <v>363</v>
+        <v>51.86273944538755</v>
       </c>
       <c r="Y15" t="n">
-        <v>363</v>
+        <v>31.39139276613435</v>
       </c>
     </row>
     <row r="16">
@@ -28557,7 +28557,7 @@
         <v>363</v>
       </c>
       <c r="H16" t="n">
-        <v>363</v>
+        <v>289.8742871805289</v>
       </c>
       <c r="I16" t="n">
         <v>170.3428326692986</v>
@@ -28566,7 +28566,7 @@
         <v>20.47989965557989</v>
       </c>
       <c r="K16" t="n">
-        <v>354.9217999457835</v>
+        <v>264.2178229814709</v>
       </c>
       <c r="L16" t="n">
         <v>363</v>
@@ -28599,7 +28599,7 @@
         <v>363</v>
       </c>
       <c r="V16" t="n">
-        <v>199.1703102162162</v>
+        <v>363</v>
       </c>
       <c r="W16" t="n">
         <v>363</v>
@@ -28715,7 +28715,7 @@
         <v>325.4900264410651</v>
       </c>
       <c r="H18" t="n">
-        <v>329.7583513373645</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
         <v>208.5358198536127</v>
@@ -28745,22 +28745,22 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>163.7823255942661</v>
+        <v>401</v>
       </c>
       <c r="S18" t="n">
-        <v>93.92947166272451</v>
+        <v>393.7801598571702</v>
       </c>
       <c r="T18" t="n">
-        <v>285.1938213641639</v>
+        <v>401</v>
       </c>
       <c r="U18" t="n">
-        <v>32.19394466584713</v>
+        <v>400.1939446658471</v>
       </c>
       <c r="V18" t="n">
-        <v>401</v>
+        <v>46.51066719152016</v>
       </c>
       <c r="W18" t="n">
-        <v>401</v>
+        <v>64.37314290982852</v>
       </c>
       <c r="X18" t="n">
         <v>401</v>
@@ -28785,13 +28785,13 @@
         <v>285.5362180555555</v>
       </c>
       <c r="E19" t="n">
+        <v>384.2028484382623</v>
+      </c>
+      <c r="F19" t="n">
         <v>401</v>
       </c>
-      <c r="F19" t="n">
-        <v>274.3828559677419</v>
-      </c>
       <c r="G19" t="n">
-        <v>353.0003555319933</v>
+        <v>401</v>
       </c>
       <c r="H19" t="n">
         <v>401</v>
@@ -28803,10 +28803,10 @@
         <v>388.4798996555799</v>
       </c>
       <c r="K19" t="n">
-        <v>264.2178229814709</v>
+        <v>401</v>
       </c>
       <c r="L19" t="n">
-        <v>392.4482183217136</v>
+        <v>401</v>
       </c>
       <c r="M19" t="n">
         <v>401</v>
@@ -28827,10 +28827,10 @@
         <v>401</v>
       </c>
       <c r="S19" t="n">
-        <v>358.7280370799046</v>
+        <v>401</v>
       </c>
       <c r="T19" t="n">
-        <v>401</v>
+        <v>209.1307960144544</v>
       </c>
       <c r="U19" t="n">
         <v>150.9469814383924</v>
@@ -28842,7 +28842,7 @@
         <v>226.3728098387097</v>
       </c>
       <c r="X19" t="n">
-        <v>401</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y19" t="n">
         <v>287.4653528494624</v>
@@ -28937,7 +28937,7 @@
         <v>16.55655664632661</v>
       </c>
       <c r="C21" t="n">
-        <v>37.63238815684525</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
         <v>347.9376868977026</v>
@@ -28997,7 +28997,7 @@
         <v>401</v>
       </c>
       <c r="W21" t="n">
-        <v>64.37314290982852</v>
+        <v>102.0055310666738</v>
       </c>
       <c r="X21" t="n">
         <v>401</v>
@@ -29013,19 +29013,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>287.1138003370787</v>
+        <v>401</v>
       </c>
       <c r="C22" t="n">
-        <v>272.7252466480447</v>
+        <v>401</v>
       </c>
       <c r="D22" t="n">
-        <v>285.5362180555555</v>
+        <v>401</v>
       </c>
       <c r="E22" t="n">
-        <v>280.9809048369565</v>
+        <v>401</v>
       </c>
       <c r="F22" t="n">
-        <v>274.3828559677419</v>
+        <v>401</v>
       </c>
       <c r="G22" t="n">
         <v>401</v>
@@ -29034,13 +29034,13 @@
         <v>401</v>
       </c>
       <c r="I22" t="n">
-        <v>401</v>
+        <v>170.3428326692986</v>
       </c>
       <c r="J22" t="n">
-        <v>312.9151361530604</v>
+        <v>20.47989965557989</v>
       </c>
       <c r="K22" t="n">
-        <v>401</v>
+        <v>264.2178229814709</v>
       </c>
       <c r="L22" t="n">
         <v>401</v>
@@ -29064,10 +29064,10 @@
         <v>401</v>
       </c>
       <c r="S22" t="n">
-        <v>401</v>
+        <v>358.7280370799046</v>
       </c>
       <c r="T22" t="n">
-        <v>401</v>
+        <v>345.3292150422913</v>
       </c>
       <c r="U22" t="n">
         <v>150.9469814383924</v>
@@ -29079,7 +29079,7 @@
         <v>226.3728098387097</v>
       </c>
       <c r="X22" t="n">
-        <v>247.4436454301076</v>
+        <v>401</v>
       </c>
       <c r="Y22" t="n">
         <v>401</v>
@@ -29174,7 +29174,7 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C24" t="n">
-        <v>36.63212442976754</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D24" t="n">
         <v>347.9376868977026</v>
@@ -29216,7 +29216,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>12.15906907442036</v>
       </c>
       <c r="R24" t="n">
         <v>401</v>
@@ -29234,7 +29234,7 @@
         <v>46.51066719151945</v>
       </c>
       <c r="W24" t="n">
-        <v>401</v>
+        <v>64.37314290982781</v>
       </c>
       <c r="X24" t="n">
         <v>51.86273944538684</v>
@@ -29259,28 +29259,28 @@
         <v>401</v>
       </c>
       <c r="E25" t="n">
-        <v>280.9809048369565</v>
+        <v>401</v>
       </c>
       <c r="F25" t="n">
-        <v>274.3828559677419</v>
+        <v>401</v>
       </c>
       <c r="G25" t="n">
-        <v>401</v>
+        <v>244.8346925136612</v>
       </c>
       <c r="H25" t="n">
-        <v>401</v>
+        <v>226.9113228229301</v>
       </c>
       <c r="I25" t="n">
-        <v>185.2723926256491</v>
+        <v>170.3428326692986</v>
       </c>
       <c r="J25" t="n">
         <v>20.47989965557989</v>
       </c>
       <c r="K25" t="n">
-        <v>264.2178229814709</v>
+        <v>401</v>
       </c>
       <c r="L25" t="n">
-        <v>392.4482183217136</v>
+        <v>401</v>
       </c>
       <c r="M25" t="n">
         <v>401</v>
@@ -29304,19 +29304,19 @@
         <v>358.7280370799046</v>
       </c>
       <c r="T25" t="n">
-        <v>209.1307960144544</v>
+        <v>401</v>
       </c>
       <c r="U25" t="n">
-        <v>150.9469814383924</v>
+        <v>401</v>
       </c>
       <c r="V25" t="n">
-        <v>401</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W25" t="n">
-        <v>401</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X25" t="n">
-        <v>401</v>
+        <v>288.7480041255632</v>
       </c>
       <c r="Y25" t="n">
         <v>401</v>
@@ -29490,7 +29490,7 @@
         <v>309</v>
       </c>
       <c r="C28" t="n">
-        <v>303.8837751039433</v>
+        <v>309</v>
       </c>
       <c r="D28" t="n">
         <v>309</v>
@@ -29511,7 +29511,7 @@
         <v>309</v>
       </c>
       <c r="J28" t="n">
-        <v>309</v>
+        <v>303.8837751039433</v>
       </c>
       <c r="K28" t="n">
         <v>309</v>
@@ -29666,7 +29666,7 @@
         <v>309</v>
       </c>
       <c r="I30" t="n">
-        <v>208.5358198536127</v>
+        <v>203.9416445213949</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -29690,7 +29690,7 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>136.6354293809033</v>
+        <v>141.2296047131211</v>
       </c>
       <c r="R30" t="n">
         <v>309</v>
@@ -29730,7 +29730,7 @@
         <v>309</v>
       </c>
       <c r="D31" t="n">
-        <v>309</v>
+        <v>303.8837751039433</v>
       </c>
       <c r="E31" t="n">
         <v>309</v>
@@ -29748,7 +29748,7 @@
         <v>309</v>
       </c>
       <c r="J31" t="n">
-        <v>303.8837751039433</v>
+        <v>309</v>
       </c>
       <c r="K31" t="n">
         <v>309</v>
@@ -29851,10 +29851,10 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>220.1596903373044</v>
+        <v>221.5853927981437</v>
       </c>
       <c r="S32" t="n">
-        <v>427</v>
+        <v>425.5742975391607</v>
       </c>
       <c r="T32" t="n">
         <v>427</v>
@@ -29885,7 +29885,7 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C33" t="n">
-        <v>137.5843295561263</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D33" t="n">
         <v>347.9376868977026</v>
@@ -29903,7 +29903,7 @@
         <v>329.7583513373645</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>208.5358198536127</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -29927,13 +29927,13 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>141.2296047131211</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>427</v>
+        <v>227.7823255942642</v>
       </c>
       <c r="S33" t="n">
-        <v>427</v>
+        <v>157.9294716627226</v>
       </c>
       <c r="T33" t="n">
         <v>100.3520671043044</v>
@@ -29945,10 +29945,10 @@
         <v>414.5106671915202</v>
       </c>
       <c r="W33" t="n">
-        <v>128.3731429098267</v>
+        <v>427</v>
       </c>
       <c r="X33" t="n">
-        <v>419.8627394453875</v>
+        <v>298.7022870683429</v>
       </c>
       <c r="Y33" t="n">
         <v>399.3913927661343</v>
@@ -29961,28 +29961,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>287.1138003370787</v>
+        <v>427</v>
       </c>
       <c r="C34" t="n">
-        <v>272.7252466480447</v>
+        <v>290.1145410678348</v>
       </c>
       <c r="D34" t="n">
+        <v>285.5362180555555</v>
+      </c>
+      <c r="E34" t="n">
         <v>427</v>
       </c>
-      <c r="E34" t="n">
-        <v>280.9809048369565</v>
-      </c>
       <c r="F34" t="n">
-        <v>343.6437669836856</v>
+        <v>274.3828559677419</v>
       </c>
       <c r="G34" t="n">
-        <v>244.8346925136612</v>
+        <v>427</v>
       </c>
       <c r="H34" t="n">
-        <v>427</v>
+        <v>226.9113228229301</v>
       </c>
       <c r="I34" t="n">
-        <v>427</v>
+        <v>170.3428326692986</v>
       </c>
       <c r="J34" t="n">
         <v>20.47989965557989</v>
@@ -30012,22 +30012,22 @@
         <v>427</v>
       </c>
       <c r="S34" t="n">
-        <v>358.7280370799046</v>
+        <v>427</v>
       </c>
       <c r="T34" t="n">
-        <v>209.1307960144544</v>
+        <v>427</v>
       </c>
       <c r="U34" t="n">
-        <v>150.9469814383924</v>
+        <v>427</v>
       </c>
       <c r="V34" t="n">
         <v>199.1703102162162</v>
       </c>
       <c r="W34" t="n">
-        <v>427</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X34" t="n">
-        <v>427</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y34" t="n">
         <v>427</v>
@@ -30122,16 +30122,16 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C36" t="n">
-        <v>361.0999124455193</v>
+        <v>83.22085732547447</v>
       </c>
       <c r="D36" t="n">
-        <v>347.9376868977026</v>
+        <v>55.9376868976952</v>
       </c>
       <c r="E36" t="n">
-        <v>50.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F36" t="n">
-        <v>47.63624233787687</v>
+        <v>47.63624233786939</v>
       </c>
       <c r="G36" t="n">
         <v>325.4900264410651</v>
@@ -30185,7 +30185,7 @@
         <v>432</v>
       </c>
       <c r="X36" t="n">
-        <v>141.9836843253279</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y36" t="n">
         <v>399.3913927661343</v>
@@ -30198,25 +30198,25 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>432</v>
+        <v>287.1138003370787</v>
       </c>
       <c r="C37" t="n">
         <v>432</v>
       </c>
       <c r="D37" t="n">
-        <v>285.5362180555555</v>
+        <v>432</v>
       </c>
       <c r="E37" t="n">
-        <v>280.9809048369565</v>
+        <v>432</v>
       </c>
       <c r="F37" t="n">
-        <v>432</v>
+        <v>274.3828559677419</v>
       </c>
       <c r="G37" t="n">
-        <v>432</v>
+        <v>244.8346925136612</v>
       </c>
       <c r="H37" t="n">
-        <v>384.0081011796486</v>
+        <v>226.9113228229301</v>
       </c>
       <c r="I37" t="n">
         <v>170.3428326692986</v>
@@ -30225,7 +30225,7 @@
         <v>20.47989965557989</v>
       </c>
       <c r="K37" t="n">
-        <v>264.2178229814709</v>
+        <v>355.6720579222321</v>
       </c>
       <c r="L37" t="n">
         <v>392.4482183217136</v>
@@ -30249,7 +30249,7 @@
         <v>432</v>
       </c>
       <c r="S37" t="n">
-        <v>358.7280370799046</v>
+        <v>432</v>
       </c>
       <c r="T37" t="n">
         <v>209.1307960144544</v>
@@ -30264,7 +30264,7 @@
         <v>432</v>
       </c>
       <c r="X37" t="n">
-        <v>247.4436454301076</v>
+        <v>432</v>
       </c>
       <c r="Y37" t="n">
         <v>432</v>
@@ -30359,16 +30359,16 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C39" t="n">
-        <v>361.0999124455193</v>
+        <v>83.22085732548879</v>
       </c>
       <c r="D39" t="n">
         <v>347.9376868977026</v>
       </c>
       <c r="E39" t="n">
-        <v>342.6720972219126</v>
+        <v>50.67209722189804</v>
       </c>
       <c r="F39" t="n">
-        <v>339.6362423378769</v>
+        <v>47.63624233786223</v>
       </c>
       <c r="G39" t="n">
         <v>325.4900264410651</v>
@@ -30401,7 +30401,7 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>141.2296047131211</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
         <v>432</v>
@@ -30413,16 +30413,16 @@
         <v>404.3520671043063</v>
       </c>
       <c r="U39" t="n">
-        <v>108.1939446658471</v>
+        <v>400.1939446658471</v>
       </c>
       <c r="V39" t="n">
-        <v>122.5106671915202</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W39" t="n">
-        <v>140.3731429098285</v>
+        <v>432</v>
       </c>
       <c r="X39" t="n">
-        <v>292.3809367023783</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y39" t="n">
         <v>399.3913927661343</v>
@@ -30447,7 +30447,7 @@
         <v>280.9809048369565</v>
       </c>
       <c r="F40" t="n">
-        <v>274.3828559677419</v>
+        <v>432</v>
       </c>
       <c r="G40" t="n">
         <v>244.8346925136612</v>
@@ -30462,10 +30462,10 @@
         <v>20.47989965557989</v>
       </c>
       <c r="K40" t="n">
-        <v>264.2178229814709</v>
+        <v>432</v>
       </c>
       <c r="L40" t="n">
-        <v>392.4482183217136</v>
+        <v>432</v>
       </c>
       <c r="M40" t="n">
         <v>432</v>
@@ -30492,19 +30492,19 @@
         <v>432</v>
       </c>
       <c r="U40" t="n">
-        <v>387.9946002198051</v>
+        <v>432</v>
       </c>
       <c r="V40" t="n">
+        <v>268.6923950713766</v>
+      </c>
+      <c r="W40" t="n">
+        <v>226.3728098387097</v>
+      </c>
+      <c r="X40" t="n">
+        <v>247.4436454301076</v>
+      </c>
+      <c r="Y40" t="n">
         <v>432</v>
-      </c>
-      <c r="W40" t="n">
-        <v>432</v>
-      </c>
-      <c r="X40" t="n">
-        <v>432</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="41">
@@ -30672,13 +30672,13 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>287.1138003370787</v>
+        <v>317</v>
       </c>
       <c r="C43" t="n">
         <v>317</v>
       </c>
       <c r="D43" t="n">
-        <v>285.5362180555555</v>
+        <v>317</v>
       </c>
       <c r="E43" t="n">
         <v>317</v>
@@ -30696,7 +30696,7 @@
         <v>317</v>
       </c>
       <c r="J43" t="n">
-        <v>110.6074940850468</v>
+        <v>49.25751247768098</v>
       </c>
       <c r="K43" t="n">
         <v>317</v>
@@ -34743,13 +34743,13 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>334</v>
+        <v>4.536310337824247</v>
       </c>
       <c r="K2" t="n">
-        <v>59.31913567839194</v>
+        <v>59.31913567839196</v>
       </c>
       <c r="L2" t="n">
-        <v>73.59063316582916</v>
+        <v>73.59063316582913</v>
       </c>
       <c r="M2" t="n">
         <v>334</v>
@@ -34758,13 +34758,13 @@
         <v>334</v>
       </c>
       <c r="O2" t="n">
-        <v>8.323768616862324</v>
+        <v>334</v>
       </c>
       <c r="P2" t="n">
         <v>66.77201533620301</v>
       </c>
       <c r="Q2" t="n">
-        <v>112.499497707764</v>
+        <v>116.2869559868019</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -34825,10 +34825,10 @@
         <v>148.7817760489965</v>
       </c>
       <c r="K3" t="n">
-        <v>194.9451151201409</v>
+        <v>231.3941565275838</v>
       </c>
       <c r="L3" t="n">
-        <v>328.266658367555</v>
+        <v>130.5062539548928</v>
       </c>
       <c r="M3" t="n">
         <v>150.1700421645043</v>
@@ -34840,7 +34840,7 @@
         <v>300.8216634121803</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>161.3113630052192</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -34877,10 +34877,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>117.8861996629213</v>
+        <v>42.97701592729238</v>
       </c>
       <c r="C4" t="n">
-        <v>57.36556961632636</v>
+        <v>132.2747533519553</v>
       </c>
       <c r="D4" t="n">
         <v>119.4637819444445</v>
@@ -34986,7 +34986,7 @@
         <v>59.31913567839196</v>
       </c>
       <c r="L5" t="n">
-        <v>181.5538205357687</v>
+        <v>73.59063316582913</v>
       </c>
       <c r="M5" t="n">
         <v>334</v>
@@ -34995,13 +34995,13 @@
         <v>334</v>
       </c>
       <c r="O5" t="n">
-        <v>8.323768616862324</v>
+        <v>183.058971323005</v>
       </c>
       <c r="P5" t="n">
-        <v>66.77201533620301</v>
+        <v>334</v>
       </c>
       <c r="Q5" t="n">
-        <v>334</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -35065,7 +35065,7 @@
         <v>231.3941565275838</v>
       </c>
       <c r="L6" t="n">
-        <v>130.5062539548928</v>
+        <v>291.817616960112</v>
       </c>
       <c r="M6" t="n">
         <v>150.1700421645043</v>
@@ -35077,7 +35077,7 @@
         <v>300.8216634121803</v>
       </c>
       <c r="P6" t="n">
-        <v>161.3113630052192</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -35114,10 +35114,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>117.8861996629213</v>
+        <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>132.2747533519553</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
         <v>119.4637819444445</v>
@@ -35129,22 +35129,22 @@
         <v>130.6171440322581</v>
       </c>
       <c r="G7" t="n">
-        <v>38.06000820988785</v>
+        <v>160.1653074863388</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>178.0886771770699</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>234.6571673307014</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>334</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>28.30590921787232</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>12.55178167828637</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -35174,16 +35174,16 @@
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>205.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>178.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>157.5563545698924</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>117.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -35223,13 +35223,13 @@
         <v>59.31913567839195</v>
       </c>
       <c r="L8" t="n">
-        <v>202.6649316468785</v>
+        <v>202.6649316468799</v>
       </c>
       <c r="M8" t="n">
-        <v>356.0000000000005</v>
+        <v>356</v>
       </c>
       <c r="N8" t="n">
-        <v>356.0000000000005</v>
+        <v>356</v>
       </c>
       <c r="O8" t="n">
         <v>8.323768616862324</v>
@@ -35238,7 +35238,7 @@
         <v>66.77201533620301</v>
       </c>
       <c r="Q8" t="n">
-        <v>356.0000000000005</v>
+        <v>356</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -35302,7 +35302,7 @@
         <v>231.3941565275838</v>
       </c>
       <c r="L9" t="n">
-        <v>217.6173650660039</v>
+        <v>328.266658367555</v>
       </c>
       <c r="M9" t="n">
         <v>150.1700421645043</v>
@@ -35314,7 +35314,7 @@
         <v>300.8216634121803</v>
       </c>
       <c r="P9" t="n">
-        <v>161.3113630052192</v>
+        <v>50.66206970366812</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -35351,7 +35351,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>117.8861996629213</v>
       </c>
       <c r="C10" t="n">
         <v>132.2747533519553</v>
@@ -35366,16 +35366,16 @@
         <v>130.6171440322581</v>
       </c>
       <c r="G10" t="n">
-        <v>160.1653074863388</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>178.0886771770699</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>234.6571673307014</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>242.582937544203</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -35408,19 +35408,19 @@
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>38.06000820988773</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>205.8296897837838</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>178.6271901612903</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>157.5563545698924</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>117.5346471505376</v>
       </c>
     </row>
     <row r="11">
@@ -35454,19 +35454,19 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>4.536310337824247</v>
+        <v>368</v>
       </c>
       <c r="K11" t="n">
-        <v>59.31913567839196</v>
+        <v>59.31913567839194</v>
       </c>
       <c r="L11" t="n">
-        <v>214.1800831620295</v>
+        <v>73.59063316582916</v>
       </c>
       <c r="M11" t="n">
-        <v>368.0000000000007</v>
+        <v>368</v>
       </c>
       <c r="N11" t="n">
-        <v>368.0000000000007</v>
+        <v>368</v>
       </c>
       <c r="O11" t="n">
         <v>8.323768616862324</v>
@@ -35475,7 +35475,7 @@
         <v>66.77201533620301</v>
       </c>
       <c r="Q11" t="n">
-        <v>368.0000000000007</v>
+        <v>145.1257603340268</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -35539,7 +35539,7 @@
         <v>231.3941565275838</v>
       </c>
       <c r="L12" t="n">
-        <v>328.266658367555</v>
+        <v>265.1325165811555</v>
       </c>
       <c r="M12" t="n">
         <v>150.1700421645043</v>
@@ -35548,7 +35548,7 @@
         <v>199.5197953916737</v>
       </c>
       <c r="O12" t="n">
-        <v>237.6875216257809</v>
+        <v>300.8216634121803</v>
       </c>
       <c r="P12" t="n">
         <v>161.3113630052192</v>
@@ -35691,19 +35691,19 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>368.0000000000007</v>
+        <v>4.536310337824247</v>
       </c>
       <c r="K14" t="n">
-        <v>59.31913567839194</v>
+        <v>59.31913567839196</v>
       </c>
       <c r="L14" t="n">
-        <v>73.59063316582916</v>
+        <v>214.1800831620317</v>
       </c>
       <c r="M14" t="n">
-        <v>145.1257603340245</v>
+        <v>368</v>
       </c>
       <c r="N14" t="n">
-        <v>368.0000000000007</v>
+        <v>368</v>
       </c>
       <c r="O14" t="n">
         <v>8.323768616862324</v>
@@ -35712,7 +35712,7 @@
         <v>66.77201533620301</v>
       </c>
       <c r="Q14" t="n">
-        <v>368.0000000000007</v>
+        <v>368</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -35785,10 +35785,10 @@
         <v>199.5197953916737</v>
       </c>
       <c r="O15" t="n">
-        <v>237.6875216257809</v>
+        <v>300.8216634121803</v>
       </c>
       <c r="P15" t="n">
-        <v>161.3113630052192</v>
+        <v>98.17722121881984</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -35843,7 +35843,7 @@
         <v>118.1653074863388</v>
       </c>
       <c r="H16" t="n">
-        <v>136.0886771770699</v>
+        <v>62.96296435759883</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -35852,7 +35852,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>90.70397696431257</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -35876,7 +35876,7 @@
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>4.271962920095384</v>
+        <v>4.271962920095405</v>
       </c>
       <c r="T16" t="n">
         <v>153.8692039855456</v>
@@ -35885,7 +35885,7 @@
         <v>212.0530185616076</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>163.8296897837838</v>
       </c>
       <c r="W16" t="n">
         <v>136.6271901612903</v>
@@ -35928,19 +35928,19 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>368.0000000000007</v>
+        <v>4.536310337824247</v>
       </c>
       <c r="K17" t="n">
-        <v>59.31913567839194</v>
+        <v>59.31913567839196</v>
       </c>
       <c r="L17" t="n">
-        <v>73.59063316582916</v>
+        <v>214.1800831620317</v>
       </c>
       <c r="M17" t="n">
-        <v>368.0000000000007</v>
+        <v>368</v>
       </c>
       <c r="N17" t="n">
-        <v>368.0000000000007</v>
+        <v>368</v>
       </c>
       <c r="O17" t="n">
         <v>8.323768616862324</v>
@@ -35949,7 +35949,7 @@
         <v>66.77201533620301</v>
       </c>
       <c r="Q17" t="n">
-        <v>145.1257603340243</v>
+        <v>368</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -36022,10 +36022,10 @@
         <v>199.5197953916737</v>
       </c>
       <c r="O18" t="n">
-        <v>300.8216634121803</v>
+        <v>237.6875216257809</v>
       </c>
       <c r="P18" t="n">
-        <v>98.17722121881984</v>
+        <v>161.3113630052192</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -36071,13 +36071,13 @@
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>120.0190951630435</v>
+        <v>103.2219436013057</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>126.6171440322581</v>
       </c>
       <c r="G19" t="n">
-        <v>108.1656630183321</v>
+        <v>156.1653074863388</v>
       </c>
       <c r="H19" t="n">
         <v>174.0886771770699</v>
@@ -36089,10 +36089,10 @@
         <v>368</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>136.7821770185291</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>8.551781678286403</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -36113,10 +36113,10 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>42.27196292009538</v>
       </c>
       <c r="T19" t="n">
-        <v>191.8692039855456</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
@@ -36128,7 +36128,7 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>153.5563545698924</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
         <v>0</v>
@@ -36165,7 +36165,7 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>368.0000000000007</v>
+        <v>368</v>
       </c>
       <c r="K20" t="n">
         <v>59.31913567839194</v>
@@ -36174,10 +36174,10 @@
         <v>73.59063316582916</v>
       </c>
       <c r="M20" t="n">
-        <v>145.1257603340245</v>
+        <v>145.1257603340268</v>
       </c>
       <c r="N20" t="n">
-        <v>368.0000000000007</v>
+        <v>368</v>
       </c>
       <c r="O20" t="n">
         <v>8.323768616862324</v>
@@ -36186,7 +36186,7 @@
         <v>66.77201533620301</v>
       </c>
       <c r="Q20" t="n">
-        <v>368.0000000000007</v>
+        <v>368</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -36250,7 +36250,7 @@
         <v>231.3941565275838</v>
       </c>
       <c r="L21" t="n">
-        <v>265.1325165811555</v>
+        <v>328.266658367555</v>
       </c>
       <c r="M21" t="n">
         <v>150.1700421645043</v>
@@ -36259,7 +36259,7 @@
         <v>199.5197953916737</v>
       </c>
       <c r="O21" t="n">
-        <v>300.8216634121803</v>
+        <v>237.6875216257809</v>
       </c>
       <c r="P21" t="n">
         <v>161.3113630052192</v>
@@ -36299,19 +36299,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0</v>
+        <v>113.8861996629213</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>128.2747533519553</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>115.4637819444445</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>120.0190951630435</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>126.6171440322581</v>
       </c>
       <c r="G22" t="n">
         <v>156.1653074863388</v>
@@ -36320,16 +36320,16 @@
         <v>174.0886771770699</v>
       </c>
       <c r="I22" t="n">
-        <v>230.6571673307014</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>292.4352364974805</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>136.7821770185291</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>8.551781678286403</v>
+        <v>8.551781678286375</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -36350,10 +36350,10 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>42.27196292009538</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>191.8692039855456</v>
+        <v>136.1984190278368</v>
       </c>
       <c r="U22" t="n">
         <v>0</v>
@@ -36365,7 +36365,7 @@
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>153.5563545698924</v>
       </c>
       <c r="Y22" t="n">
         <v>113.5346471505376</v>
@@ -36405,22 +36405,22 @@
         <v>4.536310337824247</v>
       </c>
       <c r="K23" t="n">
-        <v>59.31913567839196</v>
+        <v>199.9085856745922</v>
       </c>
       <c r="L23" t="n">
-        <v>73.59063316582915</v>
+        <v>73.59063316582916</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>368.0000000000007</v>
       </c>
       <c r="N23" t="n">
-        <v>215.6852339492657</v>
+        <v>368.0000000000007</v>
       </c>
       <c r="O23" t="n">
-        <v>368.0000000000007</v>
+        <v>8.323768616862324</v>
       </c>
       <c r="P23" t="n">
-        <v>368.0000000000007</v>
+        <v>66.77201533620301</v>
       </c>
       <c r="Q23" t="n">
         <v>368.0000000000007</v>
@@ -36496,10 +36496,10 @@
         <v>199.5197953916737</v>
       </c>
       <c r="O24" t="n">
-        <v>237.6875216257809</v>
+        <v>300.8216634121803</v>
       </c>
       <c r="P24" t="n">
-        <v>161.3113630052192</v>
+        <v>98.17722121881984</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -36545,28 +36545,28 @@
         <v>115.4637819444445</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>120.0190951630435</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>126.6171440322581</v>
       </c>
       <c r="G25" t="n">
-        <v>156.1653074863388</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>174.0886771770699</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>14.92955995635053</v>
+        <v>0</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>136.7821770185291</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>8.551781678286403</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
@@ -36590,19 +36590,19 @@
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>191.8692039855456</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>250.0530185616076</v>
       </c>
       <c r="V25" t="n">
-        <v>201.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>174.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>153.5563545698924</v>
+        <v>41.30435869545559</v>
       </c>
       <c r="Y25" t="n">
         <v>113.5346471505376</v>
@@ -36639,13 +36639,13 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>326</v>
+        <v>4.536310337824247</v>
       </c>
       <c r="K26" t="n">
-        <v>59.31913567839194</v>
+        <v>59.31913567839197</v>
       </c>
       <c r="L26" t="n">
-        <v>73.59063316582916</v>
+        <v>173.8770528590012</v>
       </c>
       <c r="M26" t="n">
         <v>326</v>
@@ -36660,7 +36660,7 @@
         <v>66.77201533620301</v>
       </c>
       <c r="Q26" t="n">
-        <v>104.8227300309962</v>
+        <v>326</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -36718,13 +36718,13 @@
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>148.7817760489965</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>4.223642805708886</v>
+        <v>231.3941565275838</v>
       </c>
       <c r="L27" t="n">
-        <v>326</v>
+        <v>247.6112623271216</v>
       </c>
       <c r="M27" t="n">
         <v>150.1700421645043</v>
@@ -36776,7 +36776,7 @@
         <v>21.88619966292134</v>
       </c>
       <c r="C28" t="n">
-        <v>31.15852845589859</v>
+        <v>36.27475335195533</v>
       </c>
       <c r="D28" t="n">
         <v>23.46378194444452</v>
@@ -36797,7 +36797,7 @@
         <v>138.6571673307014</v>
       </c>
       <c r="J28" t="n">
-        <v>288.5201003444201</v>
+        <v>283.4038754483634</v>
       </c>
       <c r="K28" t="n">
         <v>44.78217701852908</v>
@@ -37016,7 +37016,7 @@
         <v>36.27475335195533</v>
       </c>
       <c r="D31" t="n">
-        <v>23.46378194444452</v>
+        <v>18.34755704838777</v>
       </c>
       <c r="E31" t="n">
         <v>28.01909516304346</v>
@@ -37034,7 +37034,7 @@
         <v>138.6571673307014</v>
       </c>
       <c r="J31" t="n">
-        <v>283.4038754483634</v>
+        <v>288.5201003444201</v>
       </c>
       <c r="K31" t="n">
         <v>44.78217701852908</v>
@@ -37113,19 +37113,19 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>4.536310337824247</v>
+        <v>304.0000000000019</v>
       </c>
       <c r="K32" t="n">
-        <v>59.31913567839196</v>
+        <v>59.31913567839194</v>
       </c>
       <c r="L32" t="n">
-        <v>304</v>
+        <v>73.59063316582916</v>
       </c>
       <c r="M32" t="n">
-        <v>152.7659417478864</v>
+        <v>304.0000000000019</v>
       </c>
       <c r="N32" t="n">
-        <v>304.0000000000019</v>
+        <v>83.71161891987957</v>
       </c>
       <c r="O32" t="n">
         <v>8.323768616862324</v>
@@ -37195,7 +37195,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>87.89430774359239</v>
+        <v>231.3941565275838</v>
       </c>
       <c r="L33" t="n">
         <v>304.0000000000019</v>
@@ -37210,7 +37210,7 @@
         <v>300.8216634121803</v>
       </c>
       <c r="P33" t="n">
-        <v>161.3113630052192</v>
+        <v>17.81151422122787</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -37247,28 +37247,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0</v>
+        <v>139.8861996629213</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>17.38929441979012</v>
       </c>
       <c r="D34" t="n">
-        <v>141.4637819444445</v>
+        <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>146.0190951630435</v>
       </c>
       <c r="F34" t="n">
-        <v>69.26091101594365</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>182.1653074863388</v>
       </c>
       <c r="H34" t="n">
-        <v>200.0886771770699</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>256.6571673307014</v>
+        <v>0</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -37298,22 +37298,22 @@
         <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>68.27196292009539</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>217.8692039855456</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>276.0530185616076</v>
       </c>
       <c r="V34" t="n">
         <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>200.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>179.5563545698924</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
         <v>139.5346471505376</v>
@@ -37356,22 +37356,22 @@
         <v>59.31913567839196</v>
       </c>
       <c r="L35" t="n">
-        <v>141.2507902327388</v>
+        <v>73.59063316582915</v>
       </c>
       <c r="M35" t="n">
-        <v>292</v>
+        <v>292.0000000000074</v>
       </c>
       <c r="N35" t="n">
-        <v>292</v>
+        <v>292.0000000000074</v>
       </c>
       <c r="O35" t="n">
-        <v>8.323768616862324</v>
+        <v>292.0000000000074</v>
       </c>
       <c r="P35" t="n">
         <v>66.77201533620301</v>
       </c>
       <c r="Q35" t="n">
-        <v>292</v>
+        <v>75.98392568374948</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -37435,19 +37435,19 @@
         <v>231.3941565275838</v>
       </c>
       <c r="L36" t="n">
-        <v>134.3362500692621</v>
+        <v>292.0000000000074</v>
       </c>
       <c r="M36" t="n">
-        <v>150.1700421645043</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
         <v>199.5197953916737</v>
       </c>
       <c r="O36" t="n">
-        <v>292</v>
+        <v>123.1949292285396</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>161.3113630052192</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -37484,25 +37484,25 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>144.8861996629213</v>
+        <v>0</v>
       </c>
       <c r="C37" t="n">
         <v>159.2747533519553</v>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
+        <v>146.4637819444445</v>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>151.0190951630435</v>
       </c>
       <c r="F37" t="n">
-        <v>157.6171440322581</v>
+        <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>187.1653074863388</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>157.0967783567186</v>
+        <v>0</v>
       </c>
       <c r="I37" t="n">
         <v>0</v>
@@ -37511,7 +37511,7 @@
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>91.45423494076113</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
@@ -37535,7 +37535,7 @@
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>73.27196292009539</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
@@ -37550,7 +37550,7 @@
         <v>205.6271901612903</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>184.5563545698924</v>
       </c>
       <c r="Y37" t="n">
         <v>144.5346471505376</v>
@@ -37590,16 +37590,16 @@
         <v>4.536310337824247</v>
       </c>
       <c r="K38" t="n">
-        <v>292</v>
+        <v>59.31913567839196</v>
       </c>
       <c r="L38" t="n">
-        <v>73.59063316582916</v>
+        <v>141.2507902326947</v>
       </c>
       <c r="M38" t="n">
-        <v>292</v>
+        <v>292.0000000000146</v>
       </c>
       <c r="N38" t="n">
-        <v>292</v>
+        <v>292.0000000000146</v>
       </c>
       <c r="O38" t="n">
         <v>8.323768616862324</v>
@@ -37608,7 +37608,7 @@
         <v>66.77201533620301</v>
       </c>
       <c r="Q38" t="n">
-        <v>126.9792927453014</v>
+        <v>292.0000000000146</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -37672,7 +37672,7 @@
         <v>231.3941565275838</v>
       </c>
       <c r="L39" t="n">
-        <v>265.0248870640428</v>
+        <v>292.0000000000146</v>
       </c>
       <c r="M39" t="n">
         <v>150.1700421645043</v>
@@ -37681,10 +37681,10 @@
         <v>199.5197953916737</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>134.3362500692475</v>
       </c>
       <c r="P39" t="n">
-        <v>161.3113630052192</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -37733,7 +37733,7 @@
         <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>157.6171440322581</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -37748,10 +37748,10 @@
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>0</v>
+        <v>167.7821770185291</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>39.5517816782864</v>
       </c>
       <c r="M40" t="n">
         <v>0</v>
@@ -37772,25 +37772,25 @@
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>73.2719629200954</v>
+        <v>73.27196292009539</v>
       </c>
       <c r="T40" t="n">
         <v>222.8692039855456</v>
       </c>
       <c r="U40" t="n">
-        <v>237.0476187814127</v>
+        <v>281.0530185616076</v>
       </c>
       <c r="V40" t="n">
-        <v>232.8296897837838</v>
+        <v>69.52208485516033</v>
       </c>
       <c r="W40" t="n">
-        <v>205.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>184.5563545698924</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>144.5346471505376</v>
       </c>
     </row>
     <row r="41">
@@ -37824,28 +37824,28 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>4.536310337824247</v>
+        <v>154.1108691873774</v>
       </c>
       <c r="K41" t="n">
-        <v>59.31913567839196</v>
+        <v>59.31913567839194</v>
       </c>
       <c r="L41" t="n">
-        <v>141.2507902327388</v>
+        <v>292</v>
       </c>
       <c r="M41" t="n">
-        <v>292</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>292</v>
+        <v>292.0000000000239</v>
       </c>
       <c r="O41" t="n">
-        <v>8.323768616862324</v>
+        <v>292.0000000000239</v>
       </c>
       <c r="P41" t="n">
         <v>66.77201533620301</v>
       </c>
       <c r="Q41" t="n">
-        <v>292</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -37906,10 +37906,10 @@
         <v>148.7817760489965</v>
       </c>
       <c r="K42" t="n">
-        <v>73.73040659684594</v>
+        <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>292</v>
+        <v>204.4190435916027</v>
       </c>
       <c r="M42" t="n">
         <v>150.1700421645043</v>
@@ -37918,10 +37918,10 @@
         <v>199.5197953916737</v>
       </c>
       <c r="O42" t="n">
-        <v>292</v>
+        <v>292.0000000000239</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>161.3113630052192</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -37958,13 +37958,13 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0</v>
+        <v>29.88619966292134</v>
       </c>
       <c r="C43" t="n">
         <v>44.27475335195533</v>
       </c>
       <c r="D43" t="n">
-        <v>0</v>
+        <v>31.46378194444452</v>
       </c>
       <c r="E43" t="n">
         <v>36.01909516304346</v>
@@ -37982,7 +37982,7 @@
         <v>146.6571673307014</v>
       </c>
       <c r="J43" t="n">
-        <v>90.12759442946688</v>
+        <v>28.77761282210109</v>
       </c>
       <c r="K43" t="n">
         <v>52.78217701852908</v>
@@ -38061,28 +38061,28 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>4.536310337824247</v>
+        <v>292.0000000000546</v>
       </c>
       <c r="K44" t="n">
-        <v>59.31913567839196</v>
+        <v>59.31913567839194</v>
       </c>
       <c r="L44" t="n">
-        <v>141.2507902327388</v>
+        <v>73.59063316582916</v>
       </c>
       <c r="M44" t="n">
-        <v>292</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>292</v>
+        <v>147.2922513576352</v>
       </c>
       <c r="O44" t="n">
-        <v>8.323768616862324</v>
+        <v>292.0000000000546</v>
       </c>
       <c r="P44" t="n">
-        <v>66.77201533620301</v>
+        <v>292.0000000000546</v>
       </c>
       <c r="Q44" t="n">
-        <v>292</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -38140,13 +38140,13 @@
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>148.7817760489965</v>
       </c>
       <c r="K45" t="n">
-        <v>231.3941565275838</v>
+        <v>73.73040659673661</v>
       </c>
       <c r="L45" t="n">
-        <v>292</v>
+        <v>292.0000000000546</v>
       </c>
       <c r="M45" t="n">
         <v>150.1700421645043</v>
@@ -38155,7 +38155,7 @@
         <v>199.5197953916737</v>
       </c>
       <c r="O45" t="n">
-        <v>283.1180261182585</v>
+        <v>292.0000000000546</v>
       </c>
       <c r="P45" t="n">
         <v>0</v>
@@ -38210,10 +38210,10 @@
         <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>28.16530748633883</v>
+        <v>28.16530748633882</v>
       </c>
       <c r="H46" t="n">
-        <v>46.08867717706991</v>
+        <v>46.0886771770699</v>
       </c>
       <c r="I46" t="n">
         <v>102.6571673307014</v>
@@ -38222,7 +38222,7 @@
         <v>252.5201003444201</v>
       </c>
       <c r="K46" t="n">
-        <v>8.782177018529069</v>
+        <v>8.782177018529087</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
